--- a/Crm/CreateDocuments/TempDoc/Dogovor_i_prilozheniia.xlsx
+++ b/Crm/CreateDocuments/TempDoc/Dogovor_i_prilozheniia.xlsx
@@ -5,23 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1\2026\2026-03-14 Данила - Диплом техникума - WPF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\1\2026\2026-03-14 Данила - Диплом техникума - WPF\Programm\Crm\CreateDocuments\TempDoc\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Договор" sheetId="6" r:id="rId1"/>
     <sheet name="Перечень" sheetId="2" r:id="rId2"/>
     <sheet name="Акт" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="209">
   <si>
     <t xml:space="preserve">и гражданин (ка) </t>
   </si>
@@ -171,72 +171,18 @@
     <t>НДС ** %,руб.</t>
   </si>
   <si>
-    <t>Наименование медицинской организации</t>
-  </si>
-  <si>
     <t>ОГРН</t>
   </si>
   <si>
-    <t>ОГРН медициснской организации</t>
-  </si>
-  <si>
     <t>ИНН</t>
   </si>
   <si>
-    <t>ИНН медицинской организации</t>
-  </si>
-  <si>
-    <t>Адрес места нахождения медициснской организации</t>
-  </si>
-  <si>
-    <t>телефон медициснской организации</t>
-  </si>
-  <si>
-    <t>О.И. Фамилия руководителя</t>
-  </si>
-  <si>
-    <t>Фамилия И.О. пациента</t>
-  </si>
-  <si>
-    <t>Адрес места жительства пациента</t>
-  </si>
-  <si>
-    <t>телефон пациента</t>
-  </si>
-  <si>
-    <t>Должность руководителя</t>
-  </si>
-  <si>
     <t>дата</t>
   </si>
   <si>
-    <t>кем текст и код подразделения</t>
-  </si>
-  <si>
-    <t>дата договора</t>
-  </si>
-  <si>
     <t>кем выдан с кодом подразделения</t>
   </si>
   <si>
-    <t>адрес проживания пациента</t>
-  </si>
-  <si>
-    <t>Сумма договора прописью</t>
-  </si>
-  <si>
-    <t>в том числе НДС сумма НДС цифрой рублей____________________________________</t>
-  </si>
-  <si>
-    <t>Фамилия И.О.</t>
-  </si>
-  <si>
-    <t>кем с кодом подразделения</t>
-  </si>
-  <si>
-    <t>№ номер договора</t>
-  </si>
-  <si>
     <t>цена услуг с НДС</t>
   </si>
   <si>
@@ -246,16 +192,10 @@
     <t>4. Настоящий Акт составлен в двух экземплярах, имеющих одинаковую юридическую силу, по одному для каждой из Сторон.</t>
   </si>
   <si>
-    <t>номер договора</t>
-  </si>
-  <si>
     <t>Преамбула договора</t>
   </si>
   <si>
     <t>1. Преамбула акта</t>
-  </si>
-  <si>
-    <t>/И.О.Фамилия/</t>
   </si>
   <si>
     <t>серия ______, номер______</t>
@@ -698,9 +638,6 @@
     <t>на оказание платных медицинских услуг</t>
   </si>
   <si>
-    <t>дата окончания договора</t>
-  </si>
-  <si>
     <t xml:space="preserve">      1.1.1. Услуги по Договору оказываются Исполнителем в соответствии с действующей лицензией на осуществление медицинской деятельности.</t>
   </si>
   <si>
@@ -710,18 +647,6 @@
     <t>- до него доведена информация о том, что граждане, находящиеся на лечении K21 в соответствии с Федеральным законом от 21 ноября 2011 г. № 323-ФЗ "Об основах охраны здоровья граждан в Российской Федерации" обязаны соблюдать режим лечения, в том числе определенный на период их временной нетрудоспособности, и правила поведения пациента в медицинских организациях.</t>
   </si>
   <si>
-    <t>дата окончания действия договора</t>
-  </si>
-  <si>
-    <t>дата начала действия договора</t>
-  </si>
-  <si>
-    <t>общая сумма договора</t>
-  </si>
-  <si>
-    <t>общая сумма договора прописью в том числе НДС цифрами</t>
-  </si>
-  <si>
     <t>1.7. В случае невозможности исполнения Исполнителем обязательств по настоящему Договору, возникшей по вине Заказчика, оплата медицинских услуг осуществляется Заказчиком в объеме фактичски понесенных Исполнителем расходов, связанных с исполнением обязательств по настоящему Договору.</t>
   </si>
   <si>
@@ -752,52 +677,103 @@
     <t>5.3. Исполнитель не несет ответственности за неисполнение или ненадлежащее исполнение настоящего Договора, причиной которого стало: нарушение Заказчиком условий настоящего Договора, несоблюдение Заказчиком рекомендаций (указаний) специалистов Исполнителя, а также по иным основаниям, предусмотренным законодательством Российской Федерации.</t>
   </si>
   <si>
-    <t>дата выдачи</t>
-  </si>
-  <si>
-    <t>адрес регистрации пациента</t>
-  </si>
-  <si>
-    <t>адрес медицинской организации</t>
-  </si>
-  <si>
     <t>Место нахождения:</t>
   </si>
   <si>
-    <t>телефон медицинской организации</t>
-  </si>
-  <si>
-    <t>факс медицинской организации</t>
-  </si>
-  <si>
     <t>Факс:</t>
   </si>
   <si>
     <t>Электронный адрес:</t>
   </si>
   <si>
-    <t>e-mail организации</t>
-  </si>
-  <si>
-    <t>ИНН организации</t>
-  </si>
-  <si>
     <t>Расчетный счет</t>
   </si>
   <si>
-    <t>РС организации</t>
-  </si>
-  <si>
     <t>БИК</t>
   </si>
   <si>
-    <t>БИК организации</t>
-  </si>
-  <si>
-    <t>ОГРН организации</t>
-  </si>
-  <si>
-    <t>И.О. Фамилия руководителя</t>
+    <t>!101!</t>
+  </si>
+  <si>
+    <t>!102!</t>
+  </si>
+  <si>
+    <t>!1!</t>
+  </si>
+  <si>
+    <t>!4!</t>
+  </si>
+  <si>
+    <t>!10!</t>
+  </si>
+  <si>
+    <t>!11!</t>
+  </si>
+  <si>
+    <t>!12!</t>
+  </si>
+  <si>
+    <t>!103!</t>
+  </si>
+  <si>
+    <t>!104!</t>
+  </si>
+  <si>
+    <t>!106!</t>
+  </si>
+  <si>
+    <t>!201!</t>
+  </si>
+  <si>
+    <t>!202!</t>
+  </si>
+  <si>
+    <t>!204!</t>
+  </si>
+  <si>
+    <t>!205!</t>
+  </si>
+  <si>
+    <t>!206!</t>
+  </si>
+  <si>
+    <t>!207!</t>
+  </si>
+  <si>
+    <t>!212!</t>
+  </si>
+  <si>
+    <t>!213!</t>
+  </si>
+  <si>
+    <t>!214!</t>
+  </si>
+  <si>
+    <t>!215!</t>
+  </si>
+  <si>
+    <t>!216!</t>
+  </si>
+  <si>
+    <t>!217!</t>
+  </si>
+  <si>
+    <t>!13!</t>
+  </si>
+  <si>
+    <t>!6!</t>
+  </si>
+  <si>
+    <t>/!1!/</t>
+  </si>
+  <si>
+    <t>№ !101!</t>
+  </si>
+  <si>
+    <t>!12!, !13!</t>
+  </si>
+  <si>
+    <t>!2!</t>
   </si>
 </sst>
 </file>
@@ -807,7 +783,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -889,6 +865,13 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -1015,9 +998,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1113,9 +1093,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1140,7 +1117,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1154,6 +1130,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1166,9 +1161,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="distributed" wrapText="1"/>
     </xf>
@@ -1184,14 +1176,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1199,18 +1194,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
@@ -1220,6 +1203,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1238,8 +1224,29 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
@@ -1251,30 +1258,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1301,59 +1284,59 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1665,8 +1648,8 @@
   <dimension ref="A1:I136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
     <col min="4" max="5" width="7.140625" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" customWidth="1"/>
@@ -1678,13 +1661,13 @@
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="67" t="s">
-        <v>70</v>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="70" t="s">
+        <v>181</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1692,7 +1675,7 @@
     </row>
     <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1723,31 +1706,31 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="56" t="s">
-        <v>59</v>
+      <c r="G4" s="71" t="s">
+        <v>182</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="76"/>
-      <c r="C5" s="76"/>
-      <c r="D5" s="76"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
+      <c r="A5" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="80"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1761,24 +1744,28 @@
       <c r="A7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="57" t="s">
+      <c r="B7" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="72" t="s">
+        <v>186</v>
+      </c>
       <c r="E7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>57</v>
+      <c r="F7" s="14" t="s">
+        <v>187</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>60</v>
+      <c r="A8" s="15" t="s">
+        <v>48</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1794,677 +1781,675 @@
         <v>4</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
+      <c r="C9" s="85" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
     </row>
     <row r="10" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="78" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="78"/>
+      <c r="I10" s="78"/>
+    </row>
+    <row r="11" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="77" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+    </row>
+    <row r="12" spans="1:9" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="81" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+    </row>
+    <row r="13" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B13" s="82"/>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+    </row>
+    <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="82" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+    </row>
+    <row r="16" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="82" t="s">
+        <v>128</v>
+      </c>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+    </row>
+    <row r="17" spans="1:9" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="83" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
+      <c r="H17" s="83"/>
+      <c r="I17" s="83"/>
+    </row>
+    <row r="18" spans="1:9" s="20" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="86"/>
+    </row>
+    <row r="19" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="87" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+    </row>
+    <row r="20" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="74"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="75" t="s">
+        <v>188</v>
+      </c>
+      <c r="E20" s="75"/>
+      <c r="F20" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="75" t="s">
+        <v>189</v>
+      </c>
+      <c r="H20" s="75"/>
+      <c r="I20" s="63"/>
+    </row>
+    <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="88" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="88"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="88"/>
+    </row>
+    <row r="22" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="74"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="90"/>
+    </row>
+    <row r="23" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+    </row>
+    <row r="24" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="88" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="88"/>
+      <c r="C24" s="88"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+    </row>
+    <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="88" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="88"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="88"/>
+      <c r="I25" s="88"/>
+    </row>
+    <row r="26" spans="1:9" s="62" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="88" t="s">
+        <v>166</v>
+      </c>
+      <c r="B26" s="88"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="88"/>
+      <c r="I26" s="88"/>
+    </row>
+    <row r="27" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="B27" s="77"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="77"/>
+      <c r="G27" s="77"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+    </row>
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="89" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="89"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+    </row>
+    <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="78" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="78"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="78"/>
+    </row>
+    <row r="30" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="82" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" s="82"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="82"/>
+      <c r="E30" s="82"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="82"/>
+      <c r="H30" s="82"/>
+      <c r="I30" s="82"/>
+    </row>
+    <row r="31" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="83"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
+    </row>
+    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="84" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="84"/>
+      <c r="C32" s="84"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="84"/>
+      <c r="F32" s="84"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+    </row>
+    <row r="33" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="76" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-    </row>
-    <row r="11" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-    </row>
-    <row r="12" spans="1:9" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-    </row>
-    <row r="13" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79" t="s">
-        <v>184</v>
-      </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
-        <v>145</v>
-      </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-    </row>
-    <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79" t="s">
-        <v>144</v>
-      </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-    </row>
-    <row r="16" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-    </row>
-    <row r="17" spans="1:9" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="80" t="s">
+      <c r="B33" s="91"/>
+      <c r="C33" s="91"/>
+      <c r="D33" s="91"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
+    </row>
+    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
+      <c r="E34" s="76"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+    </row>
+    <row r="35" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="76" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+    </row>
+    <row r="36" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+    </row>
+    <row r="37" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="76" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+    </row>
+    <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="76"/>
+      <c r="C38" s="76"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+    </row>
+    <row r="39" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="76"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+    </row>
+    <row r="40" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="76" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="76"/>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
+      <c r="I40" s="76"/>
+    </row>
+    <row r="41" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="76" t="s">
         <v>152</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-    </row>
-    <row r="18" spans="1:9" s="21" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="88" t="s">
-        <v>185</v>
-      </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="88"/>
-    </row>
-    <row r="19" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="89" t="s">
-        <v>186</v>
-      </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="89"/>
-      <c r="G19" s="89"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="89"/>
-    </row>
-    <row r="20" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="84" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" s="84"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="85" t="s">
-        <v>188</v>
-      </c>
-      <c r="E20" s="85"/>
-      <c r="F20" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="G20" s="85" t="s">
-        <v>187</v>
-      </c>
-      <c r="H20" s="85"/>
-      <c r="I20" s="65"/>
-    </row>
-    <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="90" t="s">
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+    </row>
+    <row r="42" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
+    </row>
+    <row r="43" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="76" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
+      <c r="I43" s="76"/>
+    </row>
+    <row r="44" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="76" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" s="76"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
+      <c r="I44" s="76"/>
+    </row>
+    <row r="45" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="76" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="76"/>
+    </row>
+    <row r="46" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="76" t="s">
         <v>167</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-      <c r="H21" s="90"/>
-      <c r="I21" s="90"/>
-    </row>
-    <row r="22" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="84" t="s">
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="76"/>
+    </row>
+    <row r="47" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="76" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="76"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
+      <c r="F47" s="76"/>
+      <c r="G47" s="76"/>
+      <c r="H47" s="76"/>
+      <c r="I47" s="76"/>
+    </row>
+    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="76"/>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
+      <c r="E48" s="76"/>
+      <c r="F48" s="76"/>
+      <c r="G48" s="76"/>
+      <c r="H48" s="76"/>
+      <c r="I48" s="76"/>
+    </row>
+    <row r="49" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" s="76"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="76"/>
+      <c r="I49" s="76"/>
+    </row>
+    <row r="50" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="76"/>
+      <c r="C50" s="76"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76"/>
+    </row>
+    <row r="51" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="76" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="76"/>
+      <c r="C51" s="76"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="84" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" s="84"/>
+      <c r="C52" s="84"/>
+      <c r="D52" s="84"/>
+      <c r="E52" s="84"/>
+      <c r="F52" s="84"/>
+      <c r="G52" s="84"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="84"/>
+    </row>
+    <row r="53" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="76"/>
+      <c r="C53" s="76"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="76"/>
+      <c r="F53" s="76"/>
+      <c r="G53" s="76"/>
+      <c r="H53" s="76"/>
+      <c r="I53" s="76"/>
+    </row>
+    <row r="54" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="82"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+    </row>
+    <row r="55" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="82" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="82"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="82"/>
+      <c r="E55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="82"/>
+      <c r="H55" s="82"/>
+      <c r="I55" s="82"/>
+    </row>
+    <row r="56" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" s="82"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="82"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="82"/>
+      <c r="I56" s="82"/>
+    </row>
+    <row r="57" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" s="82"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="82"/>
+      <c r="E57" s="82"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="82"/>
+      <c r="H57" s="82"/>
+      <c r="I57" s="82"/>
+    </row>
+    <row r="58" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="82" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="86" t="s">
-        <v>189</v>
-      </c>
-      <c r="I22" s="86"/>
-    </row>
-    <row r="23" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="86" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="86"/>
-      <c r="E23" s="86"/>
-      <c r="F23" s="86"/>
-      <c r="G23" s="86"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="86"/>
-    </row>
-    <row r="24" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="90" t="s">
-        <v>168</v>
-      </c>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-    </row>
-    <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="90" t="s">
-        <v>169</v>
-      </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="90"/>
-      <c r="H25" s="90"/>
-      <c r="I25" s="90"/>
-    </row>
-    <row r="26" spans="1:9" s="64" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="90" t="s">
-        <v>191</v>
-      </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="90"/>
-      <c r="I26" s="90"/>
-    </row>
-    <row r="27" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="73" t="s">
-        <v>140</v>
-      </c>
-      <c r="B27" s="73"/>
-      <c r="C27" s="73"/>
-      <c r="D27" s="73"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
-    </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="91" t="s">
-        <v>139</v>
-      </c>
-      <c r="B28" s="91"/>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-    </row>
-    <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="74" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" s="74"/>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
-    </row>
-    <row r="30" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="79" t="s">
-        <v>195</v>
-      </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-    </row>
-    <row r="31" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="80" t="s">
-        <v>170</v>
-      </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="80"/>
-      <c r="H31" s="80"/>
-      <c r="I31" s="80"/>
-    </row>
-    <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="81" t="s">
-        <v>137</v>
-      </c>
-      <c r="B32" s="81"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-    </row>
-    <row r="33" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="77" t="s">
-        <v>171</v>
-      </c>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="87"/>
-      <c r="I33" s="87"/>
-    </row>
-    <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="77" t="s">
-        <v>153</v>
-      </c>
-      <c r="B34" s="77"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-    </row>
-    <row r="35" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="77" t="s">
-        <v>136</v>
-      </c>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-    </row>
-    <row r="36" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="77" t="s">
-        <v>135</v>
-      </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-    </row>
-    <row r="37" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="77" t="s">
-        <v>134</v>
-      </c>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-    </row>
-    <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="77" t="s">
-        <v>133</v>
-      </c>
-      <c r="B38" s="77"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-    </row>
-    <row r="39" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="77" t="s">
-        <v>154</v>
-      </c>
-      <c r="B39" s="77"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-    </row>
-    <row r="40" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="77" t="s">
-        <v>155</v>
-      </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-    </row>
-    <row r="41" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="B41" s="77"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-    </row>
-    <row r="42" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="s">
-        <v>132</v>
-      </c>
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-    </row>
-    <row r="43" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="77" t="s">
-        <v>173</v>
-      </c>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-    </row>
-    <row r="44" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="77" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
-    </row>
-    <row r="45" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="77" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="77"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="77"/>
-    </row>
-    <row r="46" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="77" t="s">
-        <v>192</v>
-      </c>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="77"/>
-    </row>
-    <row r="47" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="77" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" s="77"/>
-      <c r="C47" s="77"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
-    </row>
-    <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="77" t="s">
-        <v>158</v>
-      </c>
-      <c r="B48" s="77"/>
-      <c r="C48" s="77"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="77"/>
-    </row>
-    <row r="49" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="77" t="s">
-        <v>131</v>
-      </c>
-      <c r="B49" s="77"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="77"/>
-      <c r="I49" s="77"/>
-    </row>
-    <row r="50" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="B50" s="77"/>
-      <c r="C50" s="77"/>
-      <c r="D50" s="77"/>
-      <c r="E50" s="77"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
-      <c r="H50" s="77"/>
-      <c r="I50" s="77"/>
-    </row>
-    <row r="51" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="B51" s="77"/>
-      <c r="C51" s="77"/>
-      <c r="D51" s="77"/>
-      <c r="E51" s="77"/>
-      <c r="F51" s="77"/>
-      <c r="G51" s="77"/>
-      <c r="H51" s="77"/>
-      <c r="I51" s="77"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="81" t="s">
-        <v>160</v>
-      </c>
-      <c r="B52" s="81"/>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-    </row>
-    <row r="53" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="77" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="77"/>
-      <c r="C53" s="77"/>
-      <c r="D53" s="77"/>
-      <c r="E53" s="77"/>
-      <c r="F53" s="77"/>
-      <c r="G53" s="77"/>
-      <c r="H53" s="77"/>
-      <c r="I53" s="77"/>
-    </row>
-    <row r="54" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="79" t="s">
-        <v>128</v>
-      </c>
-      <c r="B54" s="79"/>
-      <c r="C54" s="79"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="79"/>
-    </row>
-    <row r="55" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" s="79"/>
-      <c r="C55" s="79"/>
-      <c r="D55" s="79"/>
-      <c r="E55" s="79"/>
-      <c r="F55" s="79"/>
-      <c r="G55" s="79"/>
-      <c r="H55" s="79"/>
-      <c r="I55" s="79"/>
-    </row>
-    <row r="56" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="79" t="s">
-        <v>126</v>
-      </c>
-      <c r="B56" s="79"/>
-      <c r="C56" s="79"/>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
-      <c r="F56" s="79"/>
-      <c r="G56" s="79"/>
-      <c r="H56" s="79"/>
-      <c r="I56" s="79"/>
-    </row>
-    <row r="57" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="79" t="s">
-        <v>125</v>
-      </c>
-      <c r="B57" s="79"/>
-      <c r="C57" s="79"/>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
-      <c r="F57" s="79"/>
-      <c r="G57" s="79"/>
-      <c r="H57" s="79"/>
-      <c r="I57" s="79"/>
-    </row>
-    <row r="58" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="B58" s="79"/>
-      <c r="C58" s="79"/>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
-      <c r="F58" s="79"/>
-      <c r="G58" s="79"/>
-      <c r="H58" s="79"/>
-      <c r="I58" s="79"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
+      <c r="H58" s="82"/>
+      <c r="I58" s="82"/>
     </row>
     <row r="59" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="B59" s="79"/>
-      <c r="C59" s="79"/>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
-      <c r="F59" s="79"/>
-      <c r="G59" s="79"/>
-      <c r="H59" s="79"/>
-      <c r="I59" s="79"/>
+      <c r="A59" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="82"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="82"/>
+      <c r="E59" s="82"/>
+      <c r="F59" s="82"/>
+      <c r="G59" s="82"/>
+      <c r="H59" s="82"/>
+      <c r="I59" s="82"/>
     </row>
     <row r="60" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="94" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="B60" s="94"/>
       <c r="C60" s="94"/>
@@ -2476,86 +2461,86 @@
       <c r="I60" s="94"/>
     </row>
     <row r="61" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="79" t="s">
-        <v>123</v>
-      </c>
-      <c r="B61" s="79"/>
-      <c r="C61" s="79"/>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
-      <c r="F61" s="79"/>
-      <c r="G61" s="79"/>
-      <c r="H61" s="79"/>
-      <c r="I61" s="79"/>
+      <c r="A61" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
+      <c r="D61" s="82"/>
+      <c r="E61" s="82"/>
+      <c r="F61" s="82"/>
+      <c r="G61" s="82"/>
+      <c r="H61" s="82"/>
+      <c r="I61" s="82"/>
     </row>
     <row r="62" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="79"/>
-      <c r="C62" s="79"/>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
-      <c r="F62" s="79"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="79"/>
-      <c r="I62" s="79"/>
+      <c r="A62" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
+      <c r="D62" s="82"/>
+      <c r="E62" s="82"/>
+      <c r="F62" s="82"/>
+      <c r="G62" s="82"/>
+      <c r="H62" s="82"/>
+      <c r="I62" s="82"/>
     </row>
     <row r="63" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="79" t="s">
-        <v>121</v>
-      </c>
-      <c r="B63" s="79"/>
-      <c r="C63" s="79"/>
-      <c r="D63" s="79"/>
-      <c r="E63" s="79"/>
-      <c r="F63" s="79"/>
-      <c r="G63" s="79"/>
-      <c r="H63" s="79"/>
-      <c r="I63" s="79"/>
+      <c r="A63" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="B63" s="82"/>
+      <c r="C63" s="82"/>
+      <c r="D63" s="82"/>
+      <c r="E63" s="82"/>
+      <c r="F63" s="82"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="82"/>
+      <c r="I63" s="82"/>
     </row>
     <row r="64" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="79" t="s">
-        <v>120</v>
-      </c>
-      <c r="B64" s="79"/>
-      <c r="C64" s="79"/>
-      <c r="D64" s="79"/>
-      <c r="E64" s="79"/>
-      <c r="F64" s="79"/>
-      <c r="G64" s="79"/>
-      <c r="H64" s="79"/>
-      <c r="I64" s="79"/>
+      <c r="A64" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="82"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="82"/>
+      <c r="H64" s="82"/>
+      <c r="I64" s="82"/>
     </row>
     <row r="65" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="80" t="s">
-        <v>119</v>
-      </c>
-      <c r="B65" s="80"/>
-      <c r="C65" s="80"/>
-      <c r="D65" s="80"/>
-      <c r="E65" s="80"/>
-      <c r="F65" s="80"/>
-      <c r="G65" s="80"/>
-      <c r="H65" s="80"/>
-      <c r="I65" s="80"/>
+      <c r="A65" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" s="83"/>
+      <c r="C65" s="83"/>
+      <c r="D65" s="83"/>
+      <c r="E65" s="83"/>
+      <c r="F65" s="83"/>
+      <c r="G65" s="83"/>
+      <c r="H65" s="83"/>
+      <c r="I65" s="83"/>
     </row>
     <row r="66" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="80"/>
-      <c r="I66" s="80"/>
+      <c r="A66" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" s="83"/>
+      <c r="C66" s="83"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="83"/>
+      <c r="G66" s="83"/>
+      <c r="H66" s="83"/>
+      <c r="I66" s="83"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="92" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B67" s="92"/>
       <c r="C67" s="92"/>
@@ -2567,359 +2552,359 @@
       <c r="I67" s="92"/>
     </row>
     <row r="68" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="79" t="s">
-        <v>116</v>
-      </c>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="79"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="79"/>
+      <c r="A68" s="82" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="82"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
+      <c r="E68" s="82"/>
+      <c r="F68" s="82"/>
+      <c r="G68" s="82"/>
+      <c r="H68" s="82"/>
+      <c r="I68" s="82"/>
     </row>
     <row r="69" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="79" t="s">
-        <v>115</v>
-      </c>
-      <c r="B69" s="79"/>
-      <c r="C69" s="79"/>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
-      <c r="F69" s="79"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="79"/>
-      <c r="I69" s="79"/>
+      <c r="A69" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="B69" s="82"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
+      <c r="E69" s="82"/>
+      <c r="F69" s="82"/>
+      <c r="G69" s="82"/>
+      <c r="H69" s="82"/>
+      <c r="I69" s="82"/>
     </row>
     <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="79" t="s">
-        <v>114</v>
-      </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
-      <c r="F70" s="79"/>
-      <c r="G70" s="79"/>
-      <c r="H70" s="79"/>
-      <c r="I70" s="79"/>
+      <c r="A70" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B70" s="82"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
+      <c r="E70" s="82"/>
+      <c r="F70" s="82"/>
+      <c r="G70" s="82"/>
+      <c r="H70" s="82"/>
+      <c r="I70" s="82"/>
     </row>
     <row r="71" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="74" t="s">
-        <v>113</v>
-      </c>
-      <c r="B71" s="74"/>
-      <c r="C71" s="74"/>
-      <c r="D71" s="74"/>
-      <c r="E71" s="74"/>
-      <c r="F71" s="74"/>
-      <c r="G71" s="74"/>
-      <c r="H71" s="74"/>
-      <c r="I71" s="74"/>
+      <c r="A71" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="78"/>
+      <c r="G71" s="78"/>
+      <c r="H71" s="78"/>
+      <c r="I71" s="78"/>
     </row>
     <row r="72" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="101" t="s">
-        <v>112</v>
-      </c>
-      <c r="B72" s="101"/>
-      <c r="C72" s="101"/>
-      <c r="D72" s="101"/>
-      <c r="E72" s="101"/>
-      <c r="F72" s="101"/>
-      <c r="G72" s="101"/>
-      <c r="H72" s="101"/>
-      <c r="I72" s="101"/>
+      <c r="A72" s="95" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="95"/>
+      <c r="C72" s="95"/>
+      <c r="D72" s="95"/>
+      <c r="E72" s="95"/>
+      <c r="F72" s="95"/>
+      <c r="G72" s="95"/>
+      <c r="H72" s="95"/>
+      <c r="I72" s="95"/>
     </row>
     <row r="73" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="79" t="s">
-        <v>193</v>
-      </c>
-      <c r="B73" s="79"/>
-      <c r="C73" s="79"/>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
-      <c r="F73" s="79"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="79"/>
-      <c r="I73" s="79"/>
+      <c r="A73" s="82" t="s">
+        <v>168</v>
+      </c>
+      <c r="B73" s="82"/>
+      <c r="C73" s="82"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="82"/>
+      <c r="F73" s="82"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="82"/>
+      <c r="I73" s="82"/>
     </row>
     <row r="74" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="80" t="s">
-        <v>196</v>
-      </c>
-      <c r="B74" s="80"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="80"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="80"/>
-      <c r="I74" s="80"/>
+      <c r="A74" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="B74" s="83"/>
+      <c r="C74" s="83"/>
+      <c r="D74" s="83"/>
+      <c r="E74" s="83"/>
+      <c r="F74" s="83"/>
+      <c r="G74" s="83"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="83"/>
     </row>
     <row r="75" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="79" t="s">
+      <c r="A75" s="82" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="82"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="82"/>
+      <c r="E75" s="82"/>
+      <c r="F75" s="82"/>
+      <c r="G75" s="82"/>
+      <c r="H75" s="82"/>
+      <c r="I75" s="82"/>
+    </row>
+    <row r="76" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" s="95"/>
+      <c r="C76" s="95"/>
+      <c r="D76" s="95"/>
+      <c r="E76" s="95"/>
+      <c r="F76" s="95"/>
+      <c r="G76" s="95"/>
+      <c r="H76" s="95"/>
+      <c r="I76" s="95"/>
+    </row>
+    <row r="77" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="82" t="s">
+        <v>174</v>
+      </c>
+      <c r="B77" s="82"/>
+      <c r="C77" s="82"/>
+      <c r="D77" s="82"/>
+      <c r="E77" s="82"/>
+      <c r="F77" s="82"/>
+      <c r="G77" s="82"/>
+      <c r="H77" s="82"/>
+      <c r="I77" s="82"/>
+    </row>
+    <row r="78" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="B78" s="82"/>
+      <c r="C78" s="82"/>
+      <c r="D78" s="82"/>
+      <c r="E78" s="82"/>
+      <c r="F78" s="82"/>
+      <c r="G78" s="82"/>
+      <c r="H78" s="82"/>
+      <c r="I78" s="82"/>
+    </row>
+    <row r="79" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="82"/>
+      <c r="C79" s="82"/>
+      <c r="D79" s="82"/>
+      <c r="E79" s="82"/>
+      <c r="F79" s="82"/>
+      <c r="G79" s="82"/>
+      <c r="H79" s="82"/>
+      <c r="I79" s="82"/>
+    </row>
+    <row r="80" spans="1:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="B80" s="82"/>
+      <c r="C80" s="82"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82"/>
+      <c r="F80" s="82"/>
+      <c r="G80" s="82"/>
+      <c r="H80" s="82"/>
+      <c r="I80" s="82"/>
+    </row>
+    <row r="81" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="96" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="96"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="96"/>
+      <c r="E81" s="96"/>
+      <c r="F81" s="96"/>
+      <c r="G81" s="96"/>
+      <c r="H81" s="96"/>
+      <c r="I81" s="96"/>
+    </row>
+    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="82" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" s="82"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
+      <c r="H82" s="82"/>
+      <c r="I82" s="82"/>
+    </row>
+    <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="83" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" s="83"/>
+      <c r="C83" s="83"/>
+      <c r="D83" s="83"/>
+      <c r="E83" s="83"/>
+      <c r="F83" s="83"/>
+      <c r="G83" s="83"/>
+      <c r="H83" s="83"/>
+      <c r="I83" s="83"/>
+    </row>
+    <row r="84" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B84" s="83"/>
+      <c r="C84" s="83"/>
+      <c r="D84" s="83"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="83"/>
+      <c r="G84" s="83"/>
+      <c r="H84" s="83"/>
+      <c r="I84" s="83"/>
+    </row>
+    <row r="85" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="82" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="82"/>
+      <c r="C85" s="82"/>
+      <c r="D85" s="82"/>
+      <c r="E85" s="82"/>
+      <c r="F85" s="82"/>
+      <c r="G85" s="82"/>
+      <c r="H85" s="82"/>
+      <c r="I85" s="82"/>
+    </row>
+    <row r="86" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="B75" s="79"/>
-      <c r="C75" s="79"/>
-      <c r="D75" s="79"/>
-      <c r="E75" s="79"/>
-      <c r="F75" s="79"/>
-      <c r="G75" s="79"/>
-      <c r="H75" s="79"/>
-      <c r="I75" s="79"/>
-    </row>
-    <row r="76" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="101" t="s">
-        <v>111</v>
-      </c>
-      <c r="B76" s="101"/>
-      <c r="C76" s="101"/>
-      <c r="D76" s="101"/>
-      <c r="E76" s="101"/>
-      <c r="F76" s="101"/>
-      <c r="G76" s="101"/>
-      <c r="H76" s="101"/>
-      <c r="I76" s="101"/>
-    </row>
-    <row r="77" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="79" t="s">
-        <v>199</v>
-      </c>
-      <c r="B77" s="79"/>
-      <c r="C77" s="79"/>
-      <c r="D77" s="79"/>
-      <c r="E77" s="79"/>
-      <c r="F77" s="79"/>
-      <c r="G77" s="79"/>
-      <c r="H77" s="79"/>
-      <c r="I77" s="79"/>
-    </row>
-    <row r="78" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="79" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" s="79"/>
-      <c r="C78" s="79"/>
-      <c r="D78" s="79"/>
-      <c r="E78" s="79"/>
-      <c r="F78" s="79"/>
-      <c r="G78" s="79"/>
-      <c r="H78" s="79"/>
-      <c r="I78" s="79"/>
-    </row>
-    <row r="79" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="79" t="s">
-        <v>163</v>
-      </c>
-      <c r="B79" s="79"/>
-      <c r="C79" s="79"/>
-      <c r="D79" s="79"/>
-      <c r="E79" s="79"/>
-      <c r="F79" s="79"/>
-      <c r="G79" s="79"/>
-      <c r="H79" s="79"/>
-      <c r="I79" s="79"/>
-    </row>
-    <row r="80" spans="1:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="79" t="s">
-        <v>176</v>
-      </c>
-      <c r="B80" s="79"/>
-      <c r="C80" s="79"/>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
-      <c r="F80" s="79"/>
-      <c r="G80" s="79"/>
-      <c r="H80" s="79"/>
-      <c r="I80" s="79"/>
-    </row>
-    <row r="81" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="B81" s="95"/>
-      <c r="C81" s="95"/>
-      <c r="D81" s="95"/>
-      <c r="E81" s="95"/>
-      <c r="F81" s="95"/>
-      <c r="G81" s="95"/>
-      <c r="H81" s="95"/>
-      <c r="I81" s="95"/>
-    </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="B82" s="79"/>
-      <c r="C82" s="79"/>
-      <c r="D82" s="79"/>
-      <c r="E82" s="79"/>
-      <c r="F82" s="79"/>
-      <c r="G82" s="79"/>
-      <c r="H82" s="79"/>
-      <c r="I82" s="79"/>
-    </row>
-    <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="80" t="s">
-        <v>197</v>
-      </c>
-      <c r="B83" s="80"/>
-      <c r="C83" s="80"/>
-      <c r="D83" s="80"/>
-      <c r="E83" s="80"/>
-      <c r="F83" s="80"/>
-      <c r="G83" s="80"/>
-      <c r="H83" s="80"/>
-      <c r="I83" s="80"/>
-    </row>
-    <row r="84" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="80" t="s">
-        <v>164</v>
-      </c>
-      <c r="B84" s="80"/>
-      <c r="C84" s="80"/>
-      <c r="D84" s="80"/>
-      <c r="E84" s="80"/>
-      <c r="F84" s="80"/>
-      <c r="G84" s="80"/>
-      <c r="H84" s="80"/>
-      <c r="I84" s="80"/>
-    </row>
-    <row r="85" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="79" t="s">
-        <v>194</v>
-      </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="79"/>
-      <c r="I85" s="79"/>
-    </row>
-    <row r="86" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="79" t="s">
-        <v>200</v>
-      </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="79"/>
-      <c r="I86" s="79"/>
+      <c r="B86" s="82"/>
+      <c r="C86" s="82"/>
+      <c r="D86" s="82"/>
+      <c r="E86" s="82"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
+      <c r="I86" s="82"/>
     </row>
     <row r="87" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="B87" s="79"/>
-      <c r="C87" s="79"/>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
-      <c r="F87" s="79"/>
-      <c r="G87" s="79"/>
-      <c r="H87" s="79"/>
-      <c r="I87" s="79"/>
+      <c r="A87" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="82"/>
+      <c r="C87" s="82"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="82"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="82"/>
+      <c r="H87" s="82"/>
+      <c r="I87" s="82"/>
     </row>
     <row r="88" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="79" t="s">
-        <v>198</v>
-      </c>
-      <c r="B88" s="79"/>
-      <c r="C88" s="79"/>
-      <c r="D88" s="79"/>
-      <c r="E88" s="79"/>
-      <c r="F88" s="79"/>
-      <c r="G88" s="79"/>
-      <c r="H88" s="79"/>
-      <c r="I88" s="79"/>
+      <c r="A88" s="82" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" s="82"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="82"/>
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
+      <c r="I88" s="82"/>
     </row>
     <row r="89" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="79" t="s">
-        <v>109</v>
-      </c>
-      <c r="B89" s="79"/>
-      <c r="C89" s="79"/>
-      <c r="D89" s="79"/>
-      <c r="E89" s="79"/>
-      <c r="F89" s="79"/>
-      <c r="G89" s="79"/>
-      <c r="H89" s="79"/>
-      <c r="I89" s="79"/>
+      <c r="A89" s="82" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" s="82"/>
+      <c r="C89" s="82"/>
+      <c r="D89" s="82"/>
+      <c r="E89" s="82"/>
+      <c r="F89" s="82"/>
+      <c r="G89" s="82"/>
+      <c r="H89" s="82"/>
+      <c r="I89" s="82"/>
     </row>
     <row r="90" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="79" t="s">
-        <v>108</v>
-      </c>
-      <c r="B90" s="79"/>
-      <c r="C90" s="79"/>
-      <c r="D90" s="79"/>
-      <c r="E90" s="79"/>
-      <c r="F90" s="79"/>
-      <c r="G90" s="79"/>
-      <c r="H90" s="79"/>
-      <c r="I90" s="79"/>
+      <c r="A90" s="82" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="82"/>
+      <c r="C90" s="82"/>
+      <c r="D90" s="82"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="82"/>
     </row>
     <row r="91" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="79" t="s">
-        <v>107</v>
-      </c>
-      <c r="B91" s="79"/>
-      <c r="C91" s="79"/>
-      <c r="D91" s="79"/>
-      <c r="E91" s="79"/>
-      <c r="F91" s="79"/>
-      <c r="G91" s="79"/>
-      <c r="H91" s="79"/>
-      <c r="I91" s="79"/>
+      <c r="A91" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="B91" s="82"/>
+      <c r="C91" s="82"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="82"/>
+      <c r="I91" s="82"/>
     </row>
     <row r="92" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="80" t="s">
-        <v>106</v>
-      </c>
-      <c r="B92" s="80"/>
-      <c r="C92" s="80"/>
-      <c r="D92" s="80"/>
-      <c r="E92" s="80"/>
-      <c r="F92" s="80"/>
-      <c r="G92" s="80"/>
-      <c r="H92" s="80"/>
-      <c r="I92" s="80"/>
+      <c r="A92" s="83" t="s">
+        <v>86</v>
+      </c>
+      <c r="B92" s="83"/>
+      <c r="C92" s="83"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="83"/>
+      <c r="F92" s="83"/>
+      <c r="G92" s="83"/>
+      <c r="H92" s="83"/>
+      <c r="I92" s="83"/>
     </row>
     <row r="93" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="80" t="s">
-        <v>105</v>
-      </c>
-      <c r="B93" s="80"/>
-      <c r="C93" s="80"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="80"/>
-      <c r="F93" s="80"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="80"/>
-      <c r="I93" s="80"/>
+      <c r="A93" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" s="83"/>
+      <c r="C93" s="83"/>
+      <c r="D93" s="83"/>
+      <c r="E93" s="83"/>
+      <c r="F93" s="83"/>
+      <c r="G93" s="83"/>
+      <c r="H93" s="83"/>
+      <c r="I93" s="83"/>
     </row>
     <row r="94" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="73" t="s">
-        <v>104</v>
-      </c>
-      <c r="B94" s="73"/>
-      <c r="C94" s="73"/>
-      <c r="D94" s="73"/>
-      <c r="E94" s="73"/>
-      <c r="F94" s="73"/>
-      <c r="G94" s="73"/>
-      <c r="H94" s="73"/>
-      <c r="I94" s="73"/>
+      <c r="A94" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="B94" s="77"/>
+      <c r="C94" s="77"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="77"/>
+      <c r="F94" s="77"/>
+      <c r="G94" s="77"/>
+      <c r="H94" s="77"/>
+      <c r="I94" s="77"/>
     </row>
     <row r="95" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="93" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="B95" s="93"/>
       <c r="C95" s="93"/>
@@ -2931,496 +2916,504 @@
       <c r="I95" s="93"/>
     </row>
     <row r="96" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="79" t="s">
-        <v>102</v>
-      </c>
-      <c r="B96" s="79"/>
-      <c r="C96" s="79"/>
-      <c r="D96" s="79"/>
-      <c r="E96" s="79"/>
-      <c r="F96" s="79"/>
-      <c r="G96" s="79"/>
-      <c r="H96" s="79"/>
-      <c r="I96" s="79"/>
+      <c r="A96" s="82" t="s">
+        <v>82</v>
+      </c>
+      <c r="B96" s="82"/>
+      <c r="C96" s="82"/>
+      <c r="D96" s="82"/>
+      <c r="E96" s="82"/>
+      <c r="F96" s="82"/>
+      <c r="G96" s="82"/>
+      <c r="H96" s="82"/>
+      <c r="I96" s="82"/>
     </row>
     <row r="97" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="79" t="s">
-        <v>101</v>
-      </c>
-      <c r="B97" s="79"/>
-      <c r="C97" s="79"/>
-      <c r="D97" s="79"/>
-      <c r="E97" s="79"/>
-      <c r="F97" s="79"/>
-      <c r="G97" s="79"/>
-      <c r="H97" s="79"/>
-      <c r="I97" s="79"/>
+      <c r="A97" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="B97" s="82"/>
+      <c r="C97" s="82"/>
+      <c r="D97" s="82"/>
+      <c r="E97" s="82"/>
+      <c r="F97" s="82"/>
+      <c r="G97" s="82"/>
+      <c r="H97" s="82"/>
+      <c r="I97" s="82"/>
     </row>
     <row r="98" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="79" t="s">
-        <v>100</v>
-      </c>
-      <c r="B98" s="79"/>
-      <c r="C98" s="79"/>
-      <c r="D98" s="79"/>
-      <c r="E98" s="79"/>
-      <c r="F98" s="79"/>
-      <c r="G98" s="79"/>
-      <c r="H98" s="79"/>
-      <c r="I98" s="79"/>
+      <c r="A98" s="82" t="s">
+        <v>80</v>
+      </c>
+      <c r="B98" s="82"/>
+      <c r="C98" s="82"/>
+      <c r="D98" s="82"/>
+      <c r="E98" s="82"/>
+      <c r="F98" s="82"/>
+      <c r="G98" s="82"/>
+      <c r="H98" s="82"/>
+      <c r="I98" s="82"/>
     </row>
     <row r="99" spans="1:9" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="79" t="s">
-        <v>99</v>
-      </c>
-      <c r="B99" s="79"/>
-      <c r="C99" s="79"/>
-      <c r="D99" s="79"/>
-      <c r="E99" s="79"/>
-      <c r="F99" s="79"/>
-      <c r="G99" s="79"/>
-      <c r="H99" s="79"/>
-      <c r="I99" s="79"/>
+      <c r="A99" s="82" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99" s="82"/>
+      <c r="C99" s="82"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="82"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="82"/>
+      <c r="H99" s="82"/>
+      <c r="I99" s="82"/>
     </row>
     <row r="100" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="79" t="s">
-        <v>98</v>
-      </c>
-      <c r="B100" s="79"/>
-      <c r="C100" s="79"/>
-      <c r="D100" s="79"/>
-      <c r="E100" s="79"/>
-      <c r="F100" s="79"/>
-      <c r="G100" s="79"/>
-      <c r="H100" s="79"/>
-      <c r="I100" s="79"/>
+      <c r="A100" s="82" t="s">
+        <v>78</v>
+      </c>
+      <c r="B100" s="82"/>
+      <c r="C100" s="82"/>
+      <c r="D100" s="82"/>
+      <c r="E100" s="82"/>
+      <c r="F100" s="82"/>
+      <c r="G100" s="82"/>
+      <c r="H100" s="82"/>
+      <c r="I100" s="82"/>
     </row>
     <row r="101" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="73" t="s">
-        <v>97</v>
-      </c>
-      <c r="B101" s="73"/>
-      <c r="C101" s="73"/>
-      <c r="D101" s="73"/>
-      <c r="E101" s="73"/>
-      <c r="F101" s="73"/>
-      <c r="G101" s="73"/>
-      <c r="H101" s="73"/>
-      <c r="I101" s="73"/>
+      <c r="A101" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="B101" s="77"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="77"/>
+      <c r="E101" s="77"/>
+      <c r="F101" s="77"/>
+      <c r="G101" s="77"/>
+      <c r="H101" s="77"/>
+      <c r="I101" s="77"/>
     </row>
     <row r="102" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="B102" s="79"/>
-      <c r="C102" s="79"/>
-      <c r="D102" s="79"/>
-      <c r="E102" s="79"/>
-      <c r="F102" s="79"/>
-      <c r="G102" s="79"/>
-      <c r="H102" s="79"/>
-      <c r="I102" s="79"/>
+      <c r="A102" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="B102" s="82"/>
+      <c r="C102" s="82"/>
+      <c r="D102" s="82"/>
+      <c r="E102" s="82"/>
+      <c r="F102" s="82"/>
+      <c r="G102" s="82"/>
+      <c r="H102" s="82"/>
+      <c r="I102" s="82"/>
     </row>
     <row r="103" spans="1:9" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="79" t="s">
-        <v>95</v>
-      </c>
-      <c r="B103" s="79"/>
-      <c r="C103" s="79"/>
-      <c r="D103" s="79"/>
-      <c r="E103" s="79"/>
-      <c r="F103" s="79"/>
-      <c r="G103" s="79"/>
-      <c r="H103" s="79"/>
-      <c r="I103" s="79"/>
+      <c r="A103" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="B103" s="82"/>
+      <c r="C103" s="82"/>
+      <c r="D103" s="82"/>
+      <c r="E103" s="82"/>
+      <c r="F103" s="82"/>
+      <c r="G103" s="82"/>
+      <c r="H103" s="82"/>
+      <c r="I103" s="82"/>
     </row>
     <row r="104" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="79" t="s">
-        <v>94</v>
-      </c>
-      <c r="B104" s="79"/>
-      <c r="C104" s="79"/>
-      <c r="D104" s="79"/>
-      <c r="E104" s="79"/>
-      <c r="F104" s="79"/>
-      <c r="G104" s="79"/>
-      <c r="H104" s="79"/>
-      <c r="I104" s="79"/>
-    </row>
-    <row r="105" spans="1:9" s="63" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="102" t="s">
-        <v>178</v>
-      </c>
-      <c r="B105" s="102"/>
-      <c r="C105" s="102"/>
-      <c r="D105" s="102"/>
-      <c r="E105" s="102"/>
-      <c r="F105" s="102"/>
-      <c r="G105" s="102"/>
-      <c r="H105" s="102"/>
-      <c r="I105" s="102"/>
+      <c r="A104" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B104" s="82"/>
+      <c r="C104" s="82"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="82"/>
+      <c r="F104" s="82"/>
+      <c r="G104" s="82"/>
+      <c r="H104" s="82"/>
+      <c r="I104" s="82"/>
+    </row>
+    <row r="105" spans="1:9" s="61" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="110" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" s="110"/>
+      <c r="C105" s="110"/>
+      <c r="D105" s="110"/>
+      <c r="E105" s="110"/>
+      <c r="F105" s="110"/>
+      <c r="G105" s="110"/>
+      <c r="H105" s="110"/>
+      <c r="I105" s="110"/>
     </row>
     <row r="106" spans="1:9" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="79" t="s">
-        <v>165</v>
-      </c>
-      <c r="B106" s="79"/>
-      <c r="C106" s="79"/>
-      <c r="D106" s="79"/>
-      <c r="E106" s="79"/>
-      <c r="F106" s="79"/>
-      <c r="G106" s="79"/>
-      <c r="H106" s="79"/>
-      <c r="I106" s="79"/>
+      <c r="A106" s="82" t="s">
+        <v>145</v>
+      </c>
+      <c r="B106" s="82"/>
+      <c r="C106" s="82"/>
+      <c r="D106" s="82"/>
+      <c r="E106" s="82"/>
+      <c r="F106" s="82"/>
+      <c r="G106" s="82"/>
+      <c r="H106" s="82"/>
+      <c r="I106" s="82"/>
     </row>
     <row r="107" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="79" t="s">
-        <v>93</v>
-      </c>
-      <c r="B107" s="79"/>
-      <c r="C107" s="79"/>
-      <c r="D107" s="79"/>
-      <c r="E107" s="79"/>
-      <c r="F107" s="79"/>
-      <c r="G107" s="79"/>
-      <c r="H107" s="79"/>
-      <c r="I107" s="79"/>
+      <c r="A107" s="82" t="s">
+        <v>73</v>
+      </c>
+      <c r="B107" s="82"/>
+      <c r="C107" s="82"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="82"/>
+      <c r="F107" s="82"/>
+      <c r="G107" s="82"/>
+      <c r="H107" s="82"/>
+      <c r="I107" s="82"/>
     </row>
     <row r="108" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="79" t="s">
-        <v>92</v>
-      </c>
-      <c r="B108" s="79"/>
-      <c r="C108" s="79"/>
-      <c r="D108" s="79"/>
-      <c r="E108" s="79"/>
-      <c r="F108" s="79"/>
-      <c r="G108" s="79"/>
-      <c r="H108" s="79"/>
-      <c r="I108" s="79"/>
+      <c r="A108" s="82" t="s">
+        <v>72</v>
+      </c>
+      <c r="B108" s="82"/>
+      <c r="C108" s="82"/>
+      <c r="D108" s="82"/>
+      <c r="E108" s="82"/>
+      <c r="F108" s="82"/>
+      <c r="G108" s="82"/>
+      <c r="H108" s="82"/>
+      <c r="I108" s="82"/>
     </row>
     <row r="109" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="101" t="s">
-        <v>91</v>
-      </c>
-      <c r="B109" s="101"/>
-      <c r="C109" s="101"/>
-      <c r="D109" s="101"/>
-      <c r="E109" s="101"/>
-      <c r="F109" s="101"/>
-      <c r="G109" s="101"/>
-      <c r="H109" s="101"/>
-      <c r="I109" s="101"/>
+      <c r="A109" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="B109" s="95"/>
+      <c r="C109" s="95"/>
+      <c r="D109" s="95"/>
+      <c r="E109" s="95"/>
+      <c r="F109" s="95"/>
+      <c r="G109" s="95"/>
+      <c r="H109" s="95"/>
+      <c r="I109" s="95"/>
     </row>
     <row r="110" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="103" t="s">
+      <c r="A110" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="B110" s="103"/>
-      <c r="C110" s="103"/>
+      <c r="B110" s="111"/>
+      <c r="C110" s="111"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="104" t="s">
-        <v>166</v>
-      </c>
-      <c r="G110" s="104"/>
-      <c r="H110" s="104"/>
-      <c r="I110" s="104"/>
+      <c r="F110" s="112" t="s">
+        <v>146</v>
+      </c>
+      <c r="G110" s="112"/>
+      <c r="H110" s="112"/>
+      <c r="I110" s="112"/>
     </row>
     <row r="111" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="111" t="s">
-        <v>90</v>
-      </c>
-      <c r="B111" s="111"/>
-      <c r="C111" s="111"/>
+      <c r="A111" s="109" t="s">
+        <v>70</v>
+      </c>
+      <c r="B111" s="109"/>
+      <c r="C111" s="109"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="62"/>
-      <c r="G111" s="62"/>
-      <c r="H111" s="62"/>
-      <c r="I111" s="62"/>
+      <c r="F111" s="60"/>
+      <c r="G111" s="60"/>
+      <c r="H111" s="60"/>
+      <c r="I111" s="60"/>
     </row>
     <row r="112" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="97"/>
-      <c r="B112" s="97"/>
-      <c r="C112" s="97"/>
+      <c r="A112" s="98" t="s">
+        <v>191</v>
+      </c>
+      <c r="B112" s="98"/>
+      <c r="C112" s="98"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="G112" s="98" t="s">
-        <v>53</v>
-      </c>
-      <c r="H112" s="98"/>
-      <c r="I112" s="98"/>
+      <c r="F112" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="G112" s="99" t="s">
+        <v>183</v>
+      </c>
+      <c r="H112" s="99"/>
+      <c r="I112" s="99"/>
     </row>
     <row r="113" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="74" t="s">
-        <v>88</v>
-      </c>
-      <c r="B113" s="74"/>
-      <c r="C113" s="74"/>
+      <c r="A113" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="B113" s="78"/>
+      <c r="C113" s="78"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G113" s="68"/>
-      <c r="H113" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="I113" s="68"/>
+      <c r="F113" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G113" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="H113" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="I113" s="65" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="114" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="97"/>
-      <c r="B114" s="97"/>
-      <c r="C114" s="97"/>
+      <c r="A114" s="98" t="s">
+        <v>192</v>
+      </c>
+      <c r="B114" s="98"/>
+      <c r="C114" s="98"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
-      <c r="F114" s="105" t="s">
-        <v>85</v>
-      </c>
-      <c r="G114" s="105"/>
-      <c r="H114" s="105"/>
-      <c r="I114" s="105"/>
+      <c r="F114" s="104" t="s">
+        <v>65</v>
+      </c>
+      <c r="G114" s="104"/>
+      <c r="H114" s="104"/>
+      <c r="I114" s="104"/>
     </row>
     <row r="115" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="B115" s="74"/>
-      <c r="C115" s="74"/>
+      <c r="A115" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B115" s="78"/>
+      <c r="C115" s="78"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="110" t="s">
-        <v>60</v>
-      </c>
-      <c r="G115" s="110"/>
-      <c r="H115" s="110"/>
-      <c r="I115" s="110"/>
+      <c r="F115" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="G115" s="108"/>
+      <c r="H115" s="108"/>
+      <c r="I115" s="108"/>
     </row>
     <row r="116" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="B116" s="74"/>
-      <c r="C116" s="74"/>
+      <c r="A116" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="B116" s="78"/>
+      <c r="C116" s="78"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="38"/>
-      <c r="G116" s="41"/>
-      <c r="H116" s="41"/>
-      <c r="I116" s="41"/>
+      <c r="F116" s="37"/>
+      <c r="G116" s="40"/>
+      <c r="H116" s="40"/>
+      <c r="I116" s="40"/>
     </row>
     <row r="117" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B117" s="74"/>
-      <c r="C117" s="74"/>
+      <c r="A117" s="78" t="s">
+        <v>62</v>
+      </c>
+      <c r="B117" s="78"/>
+      <c r="C117" s="78"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="105" t="s">
-        <v>81</v>
-      </c>
-      <c r="G117" s="105"/>
-      <c r="H117" s="107" t="s">
-        <v>201</v>
-      </c>
-      <c r="I117" s="108"/>
+      <c r="F117" s="104" t="s">
+        <v>61</v>
+      </c>
+      <c r="G117" s="104"/>
+      <c r="H117" s="106" t="s">
+        <v>187</v>
+      </c>
+      <c r="I117" s="107"/>
     </row>
     <row r="118" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="B118" s="74"/>
-      <c r="C118" s="74"/>
+      <c r="A118" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="B118" s="78"/>
+      <c r="C118" s="78"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
-      <c r="F118" s="106" t="s">
-        <v>79</v>
-      </c>
-      <c r="G118" s="106"/>
-      <c r="H118" s="41"/>
-      <c r="I118" s="41"/>
+      <c r="F118" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="G118" s="102"/>
+      <c r="H118" s="40"/>
+      <c r="I118" s="40"/>
     </row>
     <row r="119" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="B119" s="74"/>
-      <c r="C119" s="74"/>
+      <c r="A119" s="78" t="s">
+        <v>176</v>
+      </c>
+      <c r="B119" s="78"/>
+      <c r="C119" s="78"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
-      <c r="F119" s="109" t="s">
-        <v>202</v>
-      </c>
-      <c r="G119" s="109"/>
-      <c r="H119" s="109"/>
-      <c r="I119" s="109"/>
+      <c r="F119" s="103" t="s">
+        <v>184</v>
+      </c>
+      <c r="G119" s="103"/>
+      <c r="H119" s="103"/>
+      <c r="I119" s="103"/>
     </row>
     <row r="120" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="97" t="s">
-        <v>203</v>
-      </c>
-      <c r="B120" s="97"/>
-      <c r="C120" s="97"/>
+      <c r="A120" s="98" t="s">
+        <v>193</v>
+      </c>
+      <c r="B120" s="98"/>
+      <c r="C120" s="98"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="105"/>
-      <c r="G120" s="105"/>
-      <c r="H120" s="105"/>
-      <c r="I120" s="105"/>
+      <c r="F120" s="104"/>
+      <c r="G120" s="104"/>
+      <c r="H120" s="104"/>
+      <c r="I120" s="104"/>
     </row>
     <row r="121" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="B121" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="C121" s="16"/>
+      <c r="A121" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C121" s="15"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
-      <c r="F121" s="106" t="s">
-        <v>78</v>
-      </c>
-      <c r="G121" s="106"/>
-      <c r="H121" s="106"/>
-      <c r="I121" s="41"/>
+      <c r="F121" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="G121" s="102"/>
+      <c r="H121" s="102"/>
+      <c r="I121" s="40"/>
     </row>
     <row r="122" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="72" t="s">
-        <v>207</v>
-      </c>
-      <c r="B122" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C122" s="72"/>
+      <c r="A122" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C122" s="69"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="26"/>
-      <c r="G122" s="41"/>
-      <c r="H122" s="41"/>
-      <c r="I122" s="41"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="40"/>
+      <c r="H122" s="40"/>
+      <c r="I122" s="40"/>
     </row>
     <row r="123" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="74" t="s">
-        <v>208</v>
-      </c>
-      <c r="B123" s="74"/>
-      <c r="C123" s="54" t="s">
-        <v>209</v>
+      <c r="A123" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="B123" s="78"/>
+      <c r="C123" s="53" t="s">
+        <v>196</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
-      <c r="F123" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="G123" s="41"/>
-      <c r="H123" s="41"/>
-      <c r="I123" s="41"/>
+      <c r="F123" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="G123" s="40"/>
+      <c r="H123" s="40"/>
+      <c r="I123" s="40"/>
     </row>
     <row r="124" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B124" s="74"/>
-      <c r="C124" s="74"/>
+      <c r="A124" s="78" t="s">
+        <v>57</v>
+      </c>
+      <c r="B124" s="78"/>
+      <c r="C124" s="78"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="G124" s="41"/>
-      <c r="H124" s="41"/>
-      <c r="I124" s="41"/>
+      <c r="F124" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="G124" s="40"/>
+      <c r="H124" s="40"/>
+      <c r="I124" s="40"/>
     </row>
     <row r="125" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B125" s="74"/>
-      <c r="C125" s="74"/>
+      <c r="A125" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B125" s="78"/>
+      <c r="C125" s="78"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="69" t="s">
-        <v>55</v>
-      </c>
-      <c r="G125" s="60"/>
-      <c r="H125" s="60"/>
-      <c r="I125" s="60"/>
+      <c r="F125" s="66" t="s">
+        <v>204</v>
+      </c>
+      <c r="G125" s="58"/>
+      <c r="H125" s="58"/>
+      <c r="I125" s="58"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="112" t="s">
-        <v>74</v>
-      </c>
-      <c r="B126" s="112"/>
-      <c r="C126" s="112"/>
+      <c r="A126" s="105" t="s">
+        <v>54</v>
+      </c>
+      <c r="B126" s="105"/>
+      <c r="C126" s="105"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
-      <c r="F126" s="59"/>
-      <c r="G126" s="59"/>
-      <c r="H126" s="59"/>
-      <c r="I126" s="59"/>
+      <c r="F126" s="57"/>
+      <c r="G126" s="57"/>
+      <c r="H126" s="57"/>
+      <c r="I126" s="57"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B127" s="49" t="s">
-        <v>210</v>
+        <v>46</v>
+      </c>
+      <c r="B127" s="48" t="s">
+        <v>197</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="28"/>
-      <c r="G127" s="35"/>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28"/>
+      <c r="F127" s="27"/>
+      <c r="G127" s="34"/>
+      <c r="H127" s="27"/>
+      <c r="I127" s="27"/>
     </row>
     <row r="128" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B128" s="49" t="s">
-        <v>212</v>
+        <v>179</v>
+      </c>
+      <c r="B128" s="48" t="s">
+        <v>198</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="100"/>
-      <c r="G128" s="100"/>
-      <c r="H128" s="100"/>
-      <c r="I128" s="100"/>
+      <c r="F128" s="101"/>
+      <c r="G128" s="101"/>
+      <c r="H128" s="101"/>
+      <c r="I128" s="101"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B129" s="49" t="s">
-        <v>214</v>
+        <v>180</v>
+      </c>
+      <c r="B129" s="48" t="s">
+        <v>199</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="99"/>
-      <c r="G129" s="99"/>
-      <c r="H129" s="99"/>
-      <c r="I129" s="99"/>
+      <c r="F129" s="100"/>
+      <c r="G129" s="100"/>
+      <c r="H129" s="100"/>
+      <c r="I129" s="100"/>
     </row>
     <row r="130" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>215</v>
+        <v>45</v>
+      </c>
+      <c r="B130" s="15" t="s">
+        <v>200</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="100"/>
-      <c r="G130" s="100"/>
-      <c r="H130" s="100"/>
-      <c r="I130" s="100"/>
+      <c r="F130" s="101"/>
+      <c r="G130" s="101"/>
+      <c r="H130" s="101"/>
+      <c r="I130" s="101"/>
     </row>
     <row r="131" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
@@ -3428,23 +3421,23 @@
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
-      <c r="F131" s="28"/>
-      <c r="G131" s="28"/>
-      <c r="H131" s="28"/>
-      <c r="I131" s="28"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
+      <c r="H131" s="27"/>
+      <c r="I131" s="27"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="49" t="s">
-        <v>56</v>
+      <c r="A132" s="48" t="s">
+        <v>201</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="28"/>
-      <c r="G132" s="28"/>
-      <c r="H132" s="28"/>
-      <c r="I132" s="28"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="27"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
@@ -3455,16 +3448,16 @@
       <c r="F133" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G133" s="71" t="s">
-        <v>53</v>
-      </c>
-      <c r="H133" s="58"/>
-      <c r="I133" s="58"/>
+      <c r="G133" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="H133" s="56"/>
+      <c r="I133" s="56"/>
     </row>
     <row r="134" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
-      <c r="B134" s="49" t="s">
-        <v>216</v>
+      <c r="B134" s="48" t="s">
+        <v>202</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
@@ -3473,10 +3466,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="10"/>
-      <c r="H134" s="96" t="s">
-        <v>73</v>
-      </c>
-      <c r="I134" s="96"/>
+      <c r="H134" s="97" t="s">
+        <v>205</v>
+      </c>
+      <c r="I134" s="97"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
@@ -3528,7 +3521,6 @@
     <mergeCell ref="A108:I108"/>
     <mergeCell ref="A87:I87"/>
     <mergeCell ref="A88:I88"/>
-    <mergeCell ref="A97:I97"/>
     <mergeCell ref="H134:I134"/>
     <mergeCell ref="A112:C112"/>
     <mergeCell ref="G112:I112"/>
@@ -3548,9 +3540,6 @@
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
     <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A100:I100"/>
-    <mergeCell ref="A98:I98"/>
-    <mergeCell ref="A99:I99"/>
     <mergeCell ref="A90:I90"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="A101:I101"/>
@@ -3562,6 +3551,10 @@
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A86:I86"/>
+    <mergeCell ref="A97:I97"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="A99:I99"/>
     <mergeCell ref="A63:I63"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A66:I66"/>
@@ -3586,19 +3579,6 @@
     <mergeCell ref="A76:I76"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="A70:I70"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A54:I54"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A33:I33"/>
     <mergeCell ref="A51:I51"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A49:I49"/>
@@ -3610,10 +3590,6 @@
     <mergeCell ref="A45:I45"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A40:I40"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A123:B123"/>
@@ -3634,11 +3610,28 @@
     <mergeCell ref="A30:I30"/>
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A54:I54"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A33:I33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="portrait" r:id="rId1"/>
@@ -3695,7 +3688,7 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="113" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="G3" s="113"/>
       <c r="H3" s="113"/>
@@ -3706,12 +3699,12 @@
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="96" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="96"/>
-      <c r="H4" s="51" t="s">
-        <v>59</v>
+      <c r="F4" s="97" t="s">
+        <v>206</v>
+      </c>
+      <c r="G4" s="97"/>
+      <c r="H4" s="50" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3727,7 +3720,7 @@
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" s="121" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C6" s="121"/>
       <c r="D6" s="121"/>
@@ -3744,7 +3737,7 @@
       <c r="E7" s="121"/>
       <c r="F7" s="121"/>
       <c r="G7" s="121"/>
-      <c r="H7" s="18"/>
+      <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
@@ -3757,108 +3750,108 @@
       <c r="H8" s="10"/>
     </row>
     <row r="9" spans="1:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="21"/>
+      <c r="H9" s="20"/>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <v>1</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="43" t="s">
+      <c r="C10" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="21"/>
+      <c r="H10" s="20"/>
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="21"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="20"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="21"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="20"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="21"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="20"/>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="21"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="20"/>
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="21"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="20"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
@@ -3868,12 +3861,12 @@
       <c r="B16" s="117"/>
       <c r="C16" s="117"/>
       <c r="D16" s="118"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="46" t="s">
+      <c r="E16" s="23"/>
+      <c r="F16" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="22"/>
-      <c r="H16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="20"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3894,7 +3887,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="17"/>
+      <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="114" t="s">
@@ -3912,47 +3905,48 @@
     </row>
     <row r="20" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="119" t="s">
-        <v>45</v>
+        <v>191</v>
       </c>
       <c r="B20" s="119"/>
       <c r="C20" s="119"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
+      <c r="F20" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="49" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>200</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="17" t="s">
+      <c r="F21" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="6" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
+      <c r="H21" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="49" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>197</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
@@ -3960,7 +3954,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -3970,36 +3964,36 @@
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
-      <c r="E23" s="82" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
+      <c r="E23" s="85" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="28" t="s">
         <v>8</v>
       </c>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="120" t="s">
-        <v>50</v>
+        <v>193</v>
       </c>
       <c r="B25" s="120"/>
       <c r="C25" s="120"/>
       <c r="D25" s="10"/>
       <c r="E25" s="115" t="s">
-        <v>54</v>
+        <v>184</v>
       </c>
       <c r="F25" s="115"/>
       <c r="G25" s="115"/>
@@ -4009,23 +4003,23 @@
       <c r="A26" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="49" t="s">
-        <v>51</v>
+      <c r="B26" s="48" t="s">
+        <v>194</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="49" t="s">
-        <v>55</v>
+      <c r="F26" s="48" t="s">
+        <v>204</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
-        <v>56</v>
+      <c r="A27" s="48" t="s">
+        <v>201</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
@@ -4036,20 +4030,20 @@
       <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="48" t="s">
-        <v>52</v>
+      <c r="A28" s="27"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="72" t="s">
+        <v>202</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10" t="s">
         <v>12</v>
       </c>
       <c r="F28" s="10"/>
-      <c r="G28" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="33"/>
+      <c r="G28" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
@@ -4115,7 +4109,7 @@
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
     <col min="7" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="5.85546875" customWidth="1"/>
@@ -4130,7 +4124,7 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="135" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H1" s="135"/>
       <c r="I1" s="135"/>
@@ -4143,7 +4137,7 @@
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="134" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="H2" s="134"/>
       <c r="I2" s="134"/>
@@ -4155,12 +4149,12 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="122" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="122"/>
-      <c r="I3" s="51" t="s">
-        <v>59</v>
+      <c r="G3" s="139" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" s="139"/>
+      <c r="I3" s="50" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4190,7 +4184,7 @@
       <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="33" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="10"/>
@@ -4199,8 +4193,8 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="52" t="s">
-        <v>183</v>
+      <c r="H6" s="51" t="s">
+        <v>189</v>
       </c>
       <c r="I6" s="10"/>
     </row>
@@ -4211,30 +4205,30 @@
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="21"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
-      <c r="F8" s="76"/>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="76"/>
+      <c r="A8" s="80" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="130" t="s">
+      <c r="A9" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="130"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="137" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="D9" s="137"/>
       <c r="E9" s="137"/>
@@ -4244,30 +4238,34 @@
       <c r="I9" s="137"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="130" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="130"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="D10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="35" t="s">
+      <c r="E10" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="F10" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="G10" s="53" t="s">
-        <v>57</v>
+      <c r="G10" s="52" t="s">
+        <v>187</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
+        <v>203</v>
+      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -4276,19 +4274,19 @@
       <c r="I11" s="10"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
-      <c r="D12" s="82" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="85" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="136" t="s">
@@ -4304,223 +4302,221 @@
       <c r="I13" s="136"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
+      <c r="A14" s="35"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
     </row>
     <row r="15" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="131" t="s">
+      <c r="A15" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="131"/>
+      <c r="B15" s="123"/>
+      <c r="C15" s="123"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="123"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="123"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="123"/>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="20" t="s">
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="19" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="42">
+      <c r="A17" s="41">
         <f>Перечень!A10</f>
         <v>1</v>
       </c>
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="42" t="s">
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="42" t="s">
-        <v>67</v>
+      <c r="H17" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="127"/>
-      <c r="C18" s="128"/>
-      <c r="D18" s="128"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="126"/>
+      <c r="D18" s="126"/>
+      <c r="E18" s="127"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
       <c r="I18" s="9"/>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="22"/>
-      <c r="B19" s="127"/>
-      <c r="C19" s="128"/>
-      <c r="D19" s="128"/>
-      <c r="E19" s="129"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="125"/>
+      <c r="C19" s="126"/>
+      <c r="D19" s="126"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" s="9"/>
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
-      <c r="B20" s="127"/>
-      <c r="C20" s="128"/>
-      <c r="D20" s="128"/>
-      <c r="E20" s="129"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="125"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="127"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
       <c r="I20" s="9"/>
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="22"/>
-      <c r="B21" s="127"/>
-      <c r="C21" s="128"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="129"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="125"/>
+      <c r="C21" s="126"/>
+      <c r="D21" s="126"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" s="9"/>
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="116" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="117"/>
       <c r="D22" s="117"/>
       <c r="E22" s="118"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="42" t="s">
-        <v>67</v>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="41" t="s">
+        <v>49</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="138" t="s">
+      <c r="A23" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="138"/>
-      <c r="C23" s="138"/>
-      <c r="D23" s="138"/>
-      <c r="E23" s="138"/>
-      <c r="F23" s="138"/>
-      <c r="G23" s="138"/>
-      <c r="H23" s="138"/>
-      <c r="I23" s="138"/>
+      <c r="B23" s="129"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="129"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="str">
+      <c r="A24" s="36" t="str">
         <f>H22</f>
         <v>цена услуг с НДС</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="139" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="139"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="G24" s="139"/>
-      <c r="H24" s="139"/>
-      <c r="I24" s="139"/>
+      <c r="C24" s="130" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="130"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="133" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="133"/>
-      <c r="I25" s="133"/>
+      <c r="A25" s="128"/>
+      <c r="B25" s="128"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="131" t="s">
+      <c r="A26" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="131"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="131"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="131"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
+      <c r="B26" s="123"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="123"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="123"/>
+      <c r="G26" s="123"/>
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
     </row>
     <row r="27" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="131" t="s">
+      <c r="A27" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="131"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
+      <c r="B27" s="123"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="123"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="123"/>
+      <c r="G27" s="123"/>
+      <c r="H27" s="123"/>
+      <c r="I27" s="123"/>
     </row>
     <row r="28" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="131" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="131"/>
-      <c r="C28" s="131"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="131"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
+      <c r="A28" s="123" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="123"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="123"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="123"/>
+      <c r="H28" s="123"/>
+      <c r="I28" s="123"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
@@ -4539,8 +4535,8 @@
       </c>
       <c r="B30" s="114"/>
       <c r="C30" s="114"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="114" t="s">
         <v>29</v>
       </c>
@@ -4549,56 +4545,60 @@
       <c r="I30" s="114"/>
     </row>
     <row r="31" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="76" t="s">
-        <v>45</v>
-      </c>
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
+      <c r="A31" s="80" t="s">
+        <v>191</v>
+      </c>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="80"/>
       <c r="E31" s="10"/>
-      <c r="F31" s="38" t="s">
+      <c r="F31" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="98" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
+      <c r="G31" s="99" t="s">
+        <v>183</v>
+      </c>
+      <c r="H31" s="99"/>
+      <c r="I31" s="99"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="49" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B32" s="48" t="s">
+        <v>200</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="6"/>
-      <c r="H32" s="39" t="s">
+      <c r="G32" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H32" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="I32" s="6"/>
+      <c r="I32" s="6" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B33" s="49" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="B33" s="48" t="s">
+        <v>197</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="28" t="s">
         <v>3</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="10"/>
@@ -4611,49 +4611,49 @@
         <v>24</v>
       </c>
       <c r="E34" s="10"/>
-      <c r="F34" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="G34" s="82"/>
-      <c r="H34" s="82"/>
-      <c r="I34" s="82"/>
+      <c r="F34" s="85" t="s">
+        <v>203</v>
+      </c>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="28" t="s">
         <v>8</v>
       </c>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="123" t="s">
+      <c r="F35" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="123"/>
-      <c r="H35" s="123"/>
-      <c r="I35" s="123"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="122"/>
     </row>
     <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="55"/>
+      <c r="A36" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="54"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="97" t="s">
-        <v>54</v>
-      </c>
-      <c r="G36" s="97"/>
-      <c r="H36" s="97"/>
-      <c r="I36" s="97"/>
+      <c r="F36" s="98" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36" s="98"/>
+      <c r="H36" s="98"/>
+      <c r="I36" s="98"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B37" s="49" t="s">
-        <v>51</v>
+      <c r="B37" s="48" t="s">
+        <v>194</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="10"/>
@@ -4661,8 +4661,8 @@
       <c r="F37" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G37" s="49" t="s">
-        <v>55</v>
+      <c r="G37" s="48" t="s">
+        <v>204</v>
       </c>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
@@ -4678,13 +4678,13 @@
       <c r="I38" s="10"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="49" t="s">
-        <v>56</v>
+      <c r="A39" s="48" t="s">
+        <v>201</v>
       </c>
       <c r="B39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="29" t="s">
+      <c r="F39" s="28" t="s">
         <v>29</v>
       </c>
       <c r="G39" s="10"/>
@@ -4692,21 +4692,21 @@
       <c r="I39" s="10"/>
     </row>
     <row r="40" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
+      <c r="A40" s="27"/>
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
-      <c r="D40" s="49" t="s">
-        <v>52</v>
+      <c r="D40" s="48" t="s">
+        <v>202</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="10"/>
-      <c r="H40" s="96" t="s">
-        <v>64</v>
-      </c>
-      <c r="I40" s="96"/>
+      <c r="H40" s="97" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="97"/>
     </row>
     <row r="41" spans="1:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="10"/>
@@ -4742,6 +4742,10 @@
     <mergeCell ref="C9:I9"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:I12"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="B16:E16"/>
@@ -4754,14 +4758,10 @@
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="A30:C30"/>
-    <mergeCell ref="C4:H4"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="G3:H3"/>
     <mergeCell ref="H40:I40"/>
     <mergeCell ref="F35:I35"/>
     <mergeCell ref="F34:I34"/>

--- a/Crm/CreateDocuments/TempDoc/Dogovor_i_prilozheniia.xlsx
+++ b/Crm/CreateDocuments/TempDoc/Dogovor_i_prilozheniia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Договор" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="210">
   <si>
     <t xml:space="preserve">и гражданин (ка) </t>
   </si>
@@ -178,9 +178,6 @@
   </si>
   <si>
     <t>дата</t>
-  </si>
-  <si>
-    <t>кем выдан с кодом подразделения</t>
   </si>
   <si>
     <t>цена услуг с НДС</t>
@@ -770,10 +767,16 @@
     <t>№ !101!</t>
   </si>
   <si>
-    <t>!12!, !13!</t>
-  </si>
-  <si>
     <t>!2!</t>
+  </si>
+  <si>
+    <t>!301!</t>
+  </si>
+  <si>
+    <t>Скидка</t>
+  </si>
+  <si>
+    <t>Итого</t>
   </si>
 </sst>
 </file>
@@ -895,7 +898,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -973,11 +976,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1007,7 +1019,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1137,6 +1148,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1149,6 +1163,21 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1164,9 +1193,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="distributed" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
@@ -1182,18 +1208,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify"/>
     </xf>
@@ -1337,6 +1351,13 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1661,13 +1682,13 @@
     <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="70" t="s">
-        <v>181</v>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="69" t="s">
+        <v>180</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1675,7 +1696,7 @@
     </row>
     <row r="2" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1706,31 +1727,31 @@
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="71" t="s">
-        <v>182</v>
+      <c r="G4" s="70" t="s">
+        <v>181</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
+      <c r="A5" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="85"/>
+      <c r="F5" s="85"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -1744,20 +1765,20 @@
       <c r="A7" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="71" t="s">
         <v>185</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>186</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1765,7 +1786,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="B8" s="11"/>
       <c r="C8" s="11"/>
@@ -1781,71 +1802,71 @@
         <v>4</v>
       </c>
       <c r="B9" s="11"/>
-      <c r="C9" s="85" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
+      <c r="C9" s="89" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="89"/>
     </row>
     <row r="10" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="78" t="s">
-        <v>131</v>
-      </c>
-      <c r="B10" s="78"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="78"/>
+      <c r="A10" s="83" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
     </row>
     <row r="11" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="77" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
+      <c r="A11" s="82" t="s">
+        <v>125</v>
+      </c>
+      <c r="B11" s="82"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
     </row>
     <row r="12" spans="1:9" ht="139.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
+      <c r="A12" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
+      <c r="H12" s="86"/>
+      <c r="I12" s="86"/>
     </row>
     <row r="13" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="82" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" s="82"/>
-      <c r="C13" s="82"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="82"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
+      <c r="A13" s="78" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="78"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="73" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="73"/>
       <c r="C14" s="73"/>
@@ -1857,105 +1878,105 @@
       <c r="I14" s="73"/>
     </row>
     <row r="15" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
+      <c r="A15" s="78" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="78"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="78"/>
     </row>
     <row r="16" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="82" t="s">
-        <v>128</v>
-      </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="82"/>
-      <c r="I16" s="82"/>
+      <c r="A16" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="78"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
     </row>
     <row r="17" spans="1:9" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-    </row>
-    <row r="18" spans="1:9" s="20" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="86" t="s">
+      <c r="A17" s="87" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" s="87"/>
+    </row>
+    <row r="18" spans="1:9" s="19" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="90" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+    </row>
+    <row r="19" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-    </row>
-    <row r="19" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="87" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
     </row>
     <row r="20" spans="1:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
       <c r="D20" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="E20" s="75"/>
+      <c r="F20" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" s="75" t="s">
         <v>188</v>
       </c>
-      <c r="E20" s="75"/>
-      <c r="F20" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" s="75" t="s">
-        <v>189</v>
-      </c>
       <c r="H20" s="75"/>
-      <c r="I20" s="63"/>
+      <c r="I20" s="62"/>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="88" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="88"/>
-      <c r="D21" s="88"/>
-      <c r="E21" s="88"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="88"/>
+      <c r="A21" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="77"/>
+      <c r="C21" s="77"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
     </row>
     <row r="22" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="74" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
@@ -1963,155 +1984,155 @@
       <c r="E22" s="74"/>
       <c r="F22" s="74"/>
       <c r="G22" s="74"/>
-      <c r="H22" s="90"/>
-      <c r="I22" s="90"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
     </row>
     <row r="23" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="90" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
+      <c r="A23" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="80"/>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="80"/>
     </row>
     <row r="24" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="77"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="77"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+    </row>
+    <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="77" t="s">
         <v>148</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="88"/>
-    </row>
-    <row r="25" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="88" t="s">
+      <c r="B25" s="77"/>
+      <c r="C25" s="77"/>
+      <c r="D25" s="77"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="77"/>
+      <c r="G25" s="77"/>
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+    </row>
+    <row r="26" spans="1:9" s="61" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="77"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="77"/>
+      <c r="G26" s="77"/>
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+    </row>
+    <row r="27" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="82" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="82"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="82"/>
+      <c r="H27" s="82"/>
+      <c r="I27" s="82"/>
+    </row>
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+    </row>
+    <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="83" t="s">
+        <v>117</v>
+      </c>
+      <c r="B29" s="83"/>
+      <c r="C29" s="83"/>
+      <c r="D29" s="83"/>
+      <c r="E29" s="83"/>
+      <c r="F29" s="83"/>
+      <c r="G29" s="83"/>
+      <c r="H29" s="83"/>
+      <c r="I29" s="83"/>
+    </row>
+    <row r="30" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="78" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="78"/>
+      <c r="C30" s="78"/>
+      <c r="D30" s="78"/>
+      <c r="E30" s="78"/>
+      <c r="F30" s="78"/>
+      <c r="G30" s="78"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+    </row>
+    <row r="31" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88"/>
-      <c r="D25" s="88"/>
-      <c r="E25" s="88"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="88"/>
-      <c r="I25" s="88"/>
-    </row>
-    <row r="26" spans="1:9" s="62" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="88" t="s">
-        <v>166</v>
-      </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="88"/>
-      <c r="H26" s="88"/>
-      <c r="I26" s="88"/>
-    </row>
-    <row r="27" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="77" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-    </row>
-    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="89" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-    </row>
-    <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="78" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-    </row>
-    <row r="30" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="82" t="s">
-        <v>170</v>
-      </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="82"/>
-      <c r="F30" s="82"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82"/>
-    </row>
-    <row r="31" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="83" t="s">
-        <v>150</v>
-      </c>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="84" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="84"/>
-      <c r="C32" s="84"/>
-      <c r="D32" s="84"/>
-      <c r="E32" s="84"/>
-      <c r="F32" s="84"/>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
+      <c r="A32" s="88" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
     </row>
     <row r="33" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="76" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" s="91"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
+        <v>150</v>
+      </c>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
     </row>
     <row r="34" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="76" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="76"/>
       <c r="C34" s="76"/>
@@ -2124,7 +2145,7 @@
     </row>
     <row r="35" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="76" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" s="76"/>
       <c r="C35" s="76"/>
@@ -2137,7 +2158,7 @@
     </row>
     <row r="36" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="76" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B36" s="76"/>
       <c r="C36" s="76"/>
@@ -2150,7 +2171,7 @@
     </row>
     <row r="37" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="76" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B37" s="76"/>
       <c r="C37" s="76"/>
@@ -2163,7 +2184,7 @@
     </row>
     <row r="38" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" s="76"/>
       <c r="C38" s="76"/>
@@ -2176,7 +2197,7 @@
     </row>
     <row r="39" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="76" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="76"/>
       <c r="C39" s="76"/>
@@ -2189,7 +2210,7 @@
     </row>
     <row r="40" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="76" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B40" s="76"/>
       <c r="C40" s="76"/>
@@ -2202,7 +2223,7 @@
     </row>
     <row r="41" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="76" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="76"/>
       <c r="C41" s="76"/>
@@ -2215,7 +2236,7 @@
     </row>
     <row r="42" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B42" s="76"/>
       <c r="C42" s="76"/>
@@ -2228,7 +2249,7 @@
     </row>
     <row r="43" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B43" s="76"/>
       <c r="C43" s="76"/>
@@ -2241,7 +2262,7 @@
     </row>
     <row r="44" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="76" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B44" s="76"/>
       <c r="C44" s="76"/>
@@ -2254,7 +2275,7 @@
     </row>
     <row r="45" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B45" s="76"/>
       <c r="C45" s="76"/>
@@ -2267,7 +2288,7 @@
     </row>
     <row r="46" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="76" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B46" s="76"/>
       <c r="C46" s="76"/>
@@ -2280,7 +2301,7 @@
     </row>
     <row r="47" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="76" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B47" s="76"/>
       <c r="C47" s="76"/>
@@ -2293,7 +2314,7 @@
     </row>
     <row r="48" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B48" s="76"/>
       <c r="C48" s="76"/>
@@ -2306,7 +2327,7 @@
     </row>
     <row r="49" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="76" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B49" s="76"/>
       <c r="C49" s="76"/>
@@ -2319,7 +2340,7 @@
     </row>
     <row r="50" spans="1:9" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="76" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B50" s="76"/>
       <c r="C50" s="76"/>
@@ -2332,7 +2353,7 @@
     </row>
     <row r="51" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="76" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B51" s="76"/>
       <c r="C51" s="76"/>
@@ -2344,21 +2365,21 @@
       <c r="I51" s="76"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="84" t="s">
-        <v>140</v>
-      </c>
-      <c r="B52" s="84"/>
-      <c r="C52" s="84"/>
-      <c r="D52" s="84"/>
-      <c r="E52" s="84"/>
-      <c r="F52" s="84"/>
-      <c r="G52" s="84"/>
-      <c r="H52" s="84"/>
-      <c r="I52" s="84"/>
+      <c r="A52" s="88" t="s">
+        <v>139</v>
+      </c>
+      <c r="B52" s="88"/>
+      <c r="C52" s="88"/>
+      <c r="D52" s="88"/>
+      <c r="E52" s="88"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="88"/>
+      <c r="H52" s="88"/>
+      <c r="I52" s="88"/>
     </row>
     <row r="53" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B53" s="76"/>
       <c r="C53" s="76"/>
@@ -2370,86 +2391,86 @@
       <c r="I53" s="76"/>
     </row>
     <row r="54" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="82" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="82"/>
-      <c r="C54" s="82"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
+      <c r="A54" s="78" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="78"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="78"/>
+      <c r="E54" s="78"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="78"/>
+      <c r="H54" s="78"/>
+      <c r="I54" s="78"/>
     </row>
     <row r="55" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="82" t="s">
-        <v>107</v>
-      </c>
-      <c r="B55" s="82"/>
-      <c r="C55" s="82"/>
-      <c r="D55" s="82"/>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
+      <c r="A55" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="78"/>
+      <c r="C55" s="78"/>
+      <c r="D55" s="78"/>
+      <c r="E55" s="78"/>
+      <c r="F55" s="78"/>
+      <c r="G55" s="78"/>
+      <c r="H55" s="78"/>
+      <c r="I55" s="78"/>
     </row>
     <row r="56" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="82" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="82"/>
-      <c r="C56" s="82"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="82"/>
-      <c r="F56" s="82"/>
-      <c r="G56" s="82"/>
-      <c r="H56" s="82"/>
-      <c r="I56" s="82"/>
+      <c r="A56" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="78"/>
+      <c r="C56" s="78"/>
+      <c r="D56" s="78"/>
+      <c r="E56" s="78"/>
+      <c r="F56" s="78"/>
+      <c r="G56" s="78"/>
+      <c r="H56" s="78"/>
+      <c r="I56" s="78"/>
     </row>
     <row r="57" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="82" t="s">
-        <v>105</v>
-      </c>
-      <c r="B57" s="82"/>
-      <c r="C57" s="82"/>
-      <c r="D57" s="82"/>
-      <c r="E57" s="82"/>
-      <c r="F57" s="82"/>
-      <c r="G57" s="82"/>
-      <c r="H57" s="82"/>
-      <c r="I57" s="82"/>
+      <c r="A57" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" s="78"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="78"/>
+      <c r="E57" s="78"/>
+      <c r="F57" s="78"/>
+      <c r="G57" s="78"/>
+      <c r="H57" s="78"/>
+      <c r="I57" s="78"/>
     </row>
     <row r="58" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="82" t="s">
-        <v>141</v>
-      </c>
-      <c r="B58" s="82"/>
-      <c r="C58" s="82"/>
-      <c r="D58" s="82"/>
-      <c r="E58" s="82"/>
-      <c r="F58" s="82"/>
-      <c r="G58" s="82"/>
-      <c r="H58" s="82"/>
-      <c r="I58" s="82"/>
+      <c r="A58" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="78"/>
+      <c r="C58" s="78"/>
+      <c r="D58" s="78"/>
+      <c r="E58" s="78"/>
+      <c r="F58" s="78"/>
+      <c r="G58" s="78"/>
+      <c r="H58" s="78"/>
+      <c r="I58" s="78"/>
     </row>
     <row r="59" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="82" t="s">
-        <v>104</v>
-      </c>
-      <c r="B59" s="82"/>
-      <c r="C59" s="82"/>
-      <c r="D59" s="82"/>
-      <c r="E59" s="82"/>
-      <c r="F59" s="82"/>
-      <c r="G59" s="82"/>
-      <c r="H59" s="82"/>
-      <c r="I59" s="82"/>
+      <c r="A59" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" s="78"/>
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="78"/>
+      <c r="F59" s="78"/>
+      <c r="G59" s="78"/>
+      <c r="H59" s="78"/>
+      <c r="I59" s="78"/>
     </row>
     <row r="60" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B60" s="94"/>
       <c r="C60" s="94"/>
@@ -2461,86 +2482,86 @@
       <c r="I60" s="94"/>
     </row>
     <row r="61" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="82" t="s">
-        <v>103</v>
-      </c>
-      <c r="B61" s="82"/>
-      <c r="C61" s="82"/>
-      <c r="D61" s="82"/>
-      <c r="E61" s="82"/>
-      <c r="F61" s="82"/>
-      <c r="G61" s="82"/>
-      <c r="H61" s="82"/>
-      <c r="I61" s="82"/>
+      <c r="A61" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="B61" s="78"/>
+      <c r="C61" s="78"/>
+      <c r="D61" s="78"/>
+      <c r="E61" s="78"/>
+      <c r="F61" s="78"/>
+      <c r="G61" s="78"/>
+      <c r="H61" s="78"/>
+      <c r="I61" s="78"/>
     </row>
     <row r="62" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="82" t="s">
-        <v>102</v>
-      </c>
-      <c r="B62" s="82"/>
-      <c r="C62" s="82"/>
-      <c r="D62" s="82"/>
-      <c r="E62" s="82"/>
-      <c r="F62" s="82"/>
-      <c r="G62" s="82"/>
-      <c r="H62" s="82"/>
-      <c r="I62" s="82"/>
+      <c r="A62" s="78" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" s="78"/>
+      <c r="C62" s="78"/>
+      <c r="D62" s="78"/>
+      <c r="E62" s="78"/>
+      <c r="F62" s="78"/>
+      <c r="G62" s="78"/>
+      <c r="H62" s="78"/>
+      <c r="I62" s="78"/>
     </row>
     <row r="63" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="82" t="s">
-        <v>101</v>
-      </c>
-      <c r="B63" s="82"/>
-      <c r="C63" s="82"/>
-      <c r="D63" s="82"/>
-      <c r="E63" s="82"/>
-      <c r="F63" s="82"/>
-      <c r="G63" s="82"/>
-      <c r="H63" s="82"/>
-      <c r="I63" s="82"/>
+      <c r="A63" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="B63" s="78"/>
+      <c r="C63" s="78"/>
+      <c r="D63" s="78"/>
+      <c r="E63" s="78"/>
+      <c r="F63" s="78"/>
+      <c r="G63" s="78"/>
+      <c r="H63" s="78"/>
+      <c r="I63" s="78"/>
     </row>
     <row r="64" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="82" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="82"/>
-      <c r="D64" s="82"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="82"/>
-      <c r="H64" s="82"/>
-      <c r="I64" s="82"/>
+      <c r="A64" s="78" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="78"/>
+      <c r="C64" s="78"/>
+      <c r="D64" s="78"/>
+      <c r="E64" s="78"/>
+      <c r="F64" s="78"/>
+      <c r="G64" s="78"/>
+      <c r="H64" s="78"/>
+      <c r="I64" s="78"/>
     </row>
     <row r="65" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="83" t="s">
-        <v>99</v>
-      </c>
-      <c r="B65" s="83"/>
-      <c r="C65" s="83"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="83"/>
-      <c r="F65" s="83"/>
-      <c r="G65" s="83"/>
-      <c r="H65" s="83"/>
-      <c r="I65" s="83"/>
+      <c r="A65" s="87" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" s="87"/>
+      <c r="C65" s="87"/>
+      <c r="D65" s="87"/>
+      <c r="E65" s="87"/>
+      <c r="F65" s="87"/>
+      <c r="G65" s="87"/>
+      <c r="H65" s="87"/>
+      <c r="I65" s="87"/>
     </row>
     <row r="66" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="83" t="s">
-        <v>98</v>
-      </c>
-      <c r="B66" s="83"/>
-      <c r="C66" s="83"/>
-      <c r="D66" s="83"/>
-      <c r="E66" s="83"/>
-      <c r="F66" s="83"/>
-      <c r="G66" s="83"/>
-      <c r="H66" s="83"/>
-      <c r="I66" s="83"/>
+      <c r="A66" s="87" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" s="87"/>
+      <c r="C66" s="87"/>
+      <c r="D66" s="87"/>
+      <c r="E66" s="87"/>
+      <c r="F66" s="87"/>
+      <c r="G66" s="87"/>
+      <c r="H66" s="87"/>
+      <c r="I66" s="87"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B67" s="92"/>
       <c r="C67" s="92"/>
@@ -2552,60 +2573,60 @@
       <c r="I67" s="92"/>
     </row>
     <row r="68" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="B68" s="82"/>
-      <c r="C68" s="82"/>
-      <c r="D68" s="82"/>
-      <c r="E68" s="82"/>
-      <c r="F68" s="82"/>
-      <c r="G68" s="82"/>
-      <c r="H68" s="82"/>
-      <c r="I68" s="82"/>
+      <c r="A68" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B68" s="78"/>
+      <c r="C68" s="78"/>
+      <c r="D68" s="78"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="78"/>
+      <c r="G68" s="78"/>
+      <c r="H68" s="78"/>
+      <c r="I68" s="78"/>
     </row>
     <row r="69" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="B69" s="82"/>
-      <c r="C69" s="82"/>
-      <c r="D69" s="82"/>
-      <c r="E69" s="82"/>
-      <c r="F69" s="82"/>
-      <c r="G69" s="82"/>
-      <c r="H69" s="82"/>
-      <c r="I69" s="82"/>
+      <c r="A69" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
+      <c r="E69" s="78"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
     </row>
     <row r="70" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="82" t="s">
-        <v>94</v>
-      </c>
-      <c r="B70" s="82"/>
-      <c r="C70" s="82"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="82"/>
-      <c r="F70" s="82"/>
-      <c r="G70" s="82"/>
-      <c r="H70" s="82"/>
-      <c r="I70" s="82"/>
+      <c r="A70" s="78" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" s="78"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="78"/>
+      <c r="E70" s="78"/>
+      <c r="F70" s="78"/>
+      <c r="G70" s="78"/>
+      <c r="H70" s="78"/>
+      <c r="I70" s="78"/>
     </row>
     <row r="71" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="78" t="s">
-        <v>93</v>
-      </c>
-      <c r="B71" s="78"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="78"/>
-      <c r="E71" s="78"/>
-      <c r="F71" s="78"/>
-      <c r="G71" s="78"/>
-      <c r="H71" s="78"/>
-      <c r="I71" s="78"/>
+      <c r="A71" s="83" t="s">
+        <v>92</v>
+      </c>
+      <c r="B71" s="83"/>
+      <c r="C71" s="83"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="83"/>
+      <c r="G71" s="83"/>
+      <c r="H71" s="83"/>
+      <c r="I71" s="83"/>
     </row>
     <row r="72" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B72" s="95"/>
       <c r="C72" s="95"/>
@@ -2617,47 +2638,47 @@
       <c r="I72" s="95"/>
     </row>
     <row r="73" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="82" t="s">
-        <v>168</v>
-      </c>
-      <c r="B73" s="82"/>
-      <c r="C73" s="82"/>
-      <c r="D73" s="82"/>
-      <c r="E73" s="82"/>
-      <c r="F73" s="82"/>
-      <c r="G73" s="82"/>
-      <c r="H73" s="82"/>
-      <c r="I73" s="82"/>
+      <c r="A73" s="78" t="s">
+        <v>167</v>
+      </c>
+      <c r="B73" s="78"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="78"/>
+      <c r="E73" s="78"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="78"/>
+      <c r="H73" s="78"/>
+      <c r="I73" s="78"/>
     </row>
     <row r="74" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="83" t="s">
-        <v>171</v>
-      </c>
-      <c r="B74" s="83"/>
-      <c r="C74" s="83"/>
-      <c r="D74" s="83"/>
-      <c r="E74" s="83"/>
-      <c r="F74" s="83"/>
-      <c r="G74" s="83"/>
-      <c r="H74" s="83"/>
-      <c r="I74" s="83"/>
+      <c r="A74" s="87" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="87"/>
+      <c r="C74" s="87"/>
+      <c r="D74" s="87"/>
+      <c r="E74" s="87"/>
+      <c r="F74" s="87"/>
+      <c r="G74" s="87"/>
+      <c r="H74" s="87"/>
+      <c r="I74" s="87"/>
     </row>
     <row r="75" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="82" t="s">
-        <v>155</v>
-      </c>
-      <c r="B75" s="82"/>
-      <c r="C75" s="82"/>
-      <c r="D75" s="82"/>
-      <c r="E75" s="82"/>
-      <c r="F75" s="82"/>
-      <c r="G75" s="82"/>
-      <c r="H75" s="82"/>
-      <c r="I75" s="82"/>
+      <c r="A75" s="78" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" s="78"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="78"/>
+      <c r="H75" s="78"/>
+      <c r="I75" s="78"/>
     </row>
     <row r="76" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B76" s="95"/>
       <c r="C76" s="95"/>
@@ -2669,60 +2690,60 @@
       <c r="I76" s="95"/>
     </row>
     <row r="77" spans="1:9" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="82" t="s">
-        <v>174</v>
-      </c>
-      <c r="B77" s="82"/>
-      <c r="C77" s="82"/>
-      <c r="D77" s="82"/>
-      <c r="E77" s="82"/>
-      <c r="F77" s="82"/>
-      <c r="G77" s="82"/>
-      <c r="H77" s="82"/>
-      <c r="I77" s="82"/>
+      <c r="A77" s="78" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" s="78"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="78"/>
+      <c r="E77" s="78"/>
+      <c r="F77" s="78"/>
+      <c r="G77" s="78"/>
+      <c r="H77" s="78"/>
+      <c r="I77" s="78"/>
     </row>
     <row r="78" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="82" t="s">
-        <v>129</v>
-      </c>
-      <c r="B78" s="82"/>
-      <c r="C78" s="82"/>
-      <c r="D78" s="82"/>
-      <c r="E78" s="82"/>
-      <c r="F78" s="82"/>
-      <c r="G78" s="82"/>
-      <c r="H78" s="82"/>
-      <c r="I78" s="82"/>
+      <c r="A78" s="78" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="78"/>
+      <c r="C78" s="78"/>
+      <c r="D78" s="78"/>
+      <c r="E78" s="78"/>
+      <c r="F78" s="78"/>
+      <c r="G78" s="78"/>
+      <c r="H78" s="78"/>
+      <c r="I78" s="78"/>
     </row>
     <row r="79" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="82" t="s">
-        <v>143</v>
-      </c>
-      <c r="B79" s="82"/>
-      <c r="C79" s="82"/>
-      <c r="D79" s="82"/>
-      <c r="E79" s="82"/>
-      <c r="F79" s="82"/>
-      <c r="G79" s="82"/>
-      <c r="H79" s="82"/>
-      <c r="I79" s="82"/>
+      <c r="A79" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B79" s="78"/>
+      <c r="C79" s="78"/>
+      <c r="D79" s="78"/>
+      <c r="E79" s="78"/>
+      <c r="F79" s="78"/>
+      <c r="G79" s="78"/>
+      <c r="H79" s="78"/>
+      <c r="I79" s="78"/>
     </row>
     <row r="80" spans="1:9" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="82" t="s">
-        <v>156</v>
-      </c>
-      <c r="B80" s="82"/>
-      <c r="C80" s="82"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="82"/>
-      <c r="F80" s="82"/>
-      <c r="G80" s="82"/>
-      <c r="H80" s="82"/>
-      <c r="I80" s="82"/>
+      <c r="A80" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" s="78"/>
+      <c r="C80" s="78"/>
+      <c r="D80" s="78"/>
+      <c r="E80" s="78"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="78"/>
+      <c r="H80" s="78"/>
+      <c r="I80" s="78"/>
     </row>
     <row r="81" spans="1:9" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="96" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B81" s="96"/>
       <c r="C81" s="96"/>
@@ -2734,177 +2755,177 @@
       <c r="I81" s="96"/>
     </row>
     <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="82" t="s">
-        <v>157</v>
-      </c>
-      <c r="B82" s="82"/>
-      <c r="C82" s="82"/>
-      <c r="D82" s="82"/>
-      <c r="E82" s="82"/>
-      <c r="F82" s="82"/>
-      <c r="G82" s="82"/>
-      <c r="H82" s="82"/>
-      <c r="I82" s="82"/>
+      <c r="A82" s="78" t="s">
+        <v>156</v>
+      </c>
+      <c r="B82" s="78"/>
+      <c r="C82" s="78"/>
+      <c r="D82" s="78"/>
+      <c r="E82" s="78"/>
+      <c r="F82" s="78"/>
+      <c r="G82" s="78"/>
+      <c r="H82" s="78"/>
+      <c r="I82" s="78"/>
     </row>
     <row r="83" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="83" t="s">
+      <c r="A83" s="87" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="87"/>
+      <c r="C83" s="87"/>
+      <c r="D83" s="87"/>
+      <c r="E83" s="87"/>
+      <c r="F83" s="87"/>
+      <c r="G83" s="87"/>
+      <c r="H83" s="87"/>
+      <c r="I83" s="87"/>
+    </row>
+    <row r="84" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="87" t="s">
+        <v>143</v>
+      </c>
+      <c r="B84" s="87"/>
+      <c r="C84" s="87"/>
+      <c r="D84" s="87"/>
+      <c r="E84" s="87"/>
+      <c r="F84" s="87"/>
+      <c r="G84" s="87"/>
+      <c r="H84" s="87"/>
+      <c r="I84" s="87"/>
+    </row>
+    <row r="85" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="78" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" s="78"/>
+      <c r="C85" s="78"/>
+      <c r="D85" s="78"/>
+      <c r="E85" s="78"/>
+      <c r="F85" s="78"/>
+      <c r="G85" s="78"/>
+      <c r="H85" s="78"/>
+      <c r="I85" s="78"/>
+    </row>
+    <row r="86" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="78" t="s">
+        <v>174</v>
+      </c>
+      <c r="B86" s="78"/>
+      <c r="C86" s="78"/>
+      <c r="D86" s="78"/>
+      <c r="E86" s="78"/>
+      <c r="F86" s="78"/>
+      <c r="G86" s="78"/>
+      <c r="H86" s="78"/>
+      <c r="I86" s="78"/>
+    </row>
+    <row r="87" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="78" t="s">
+        <v>129</v>
+      </c>
+      <c r="B87" s="78"/>
+      <c r="C87" s="78"/>
+      <c r="D87" s="78"/>
+      <c r="E87" s="78"/>
+      <c r="F87" s="78"/>
+      <c r="G87" s="78"/>
+      <c r="H87" s="78"/>
+      <c r="I87" s="78"/>
+    </row>
+    <row r="88" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="78" t="s">
         <v>172</v>
       </c>
-      <c r="B83" s="83"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
-      <c r="E83" s="83"/>
-      <c r="F83" s="83"/>
-      <c r="G83" s="83"/>
-      <c r="H83" s="83"/>
-      <c r="I83" s="83"/>
-    </row>
-    <row r="84" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="B84" s="83"/>
-      <c r="C84" s="83"/>
-      <c r="D84" s="83"/>
-      <c r="E84" s="83"/>
-      <c r="F84" s="83"/>
-      <c r="G84" s="83"/>
-      <c r="H84" s="83"/>
-      <c r="I84" s="83"/>
-    </row>
-    <row r="85" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="82" t="s">
-        <v>169</v>
-      </c>
-      <c r="B85" s="82"/>
-      <c r="C85" s="82"/>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
-      <c r="H85" s="82"/>
-      <c r="I85" s="82"/>
-    </row>
-    <row r="86" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="82" t="s">
-        <v>175</v>
-      </c>
-      <c r="B86" s="82"/>
-      <c r="C86" s="82"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="82"/>
-      <c r="F86" s="82"/>
-      <c r="G86" s="82"/>
-      <c r="H86" s="82"/>
-      <c r="I86" s="82"/>
-    </row>
-    <row r="87" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="82" t="s">
-        <v>130</v>
-      </c>
-      <c r="B87" s="82"/>
-      <c r="C87" s="82"/>
-      <c r="D87" s="82"/>
-      <c r="E87" s="82"/>
-      <c r="F87" s="82"/>
-      <c r="G87" s="82"/>
-      <c r="H87" s="82"/>
-      <c r="I87" s="82"/>
-    </row>
-    <row r="88" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="82" t="s">
-        <v>173</v>
-      </c>
-      <c r="B88" s="82"/>
-      <c r="C88" s="82"/>
-      <c r="D88" s="82"/>
-      <c r="E88" s="82"/>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="82"/>
-      <c r="I88" s="82"/>
+      <c r="B88" s="78"/>
+      <c r="C88" s="78"/>
+      <c r="D88" s="78"/>
+      <c r="E88" s="78"/>
+      <c r="F88" s="78"/>
+      <c r="G88" s="78"/>
+      <c r="H88" s="78"/>
+      <c r="I88" s="78"/>
     </row>
     <row r="89" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="B89" s="82"/>
-      <c r="C89" s="82"/>
-      <c r="D89" s="82"/>
-      <c r="E89" s="82"/>
-      <c r="F89" s="82"/>
-      <c r="G89" s="82"/>
-      <c r="H89" s="82"/>
-      <c r="I89" s="82"/>
+      <c r="A89" s="78" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" s="78"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="78"/>
+      <c r="E89" s="78"/>
+      <c r="F89" s="78"/>
+      <c r="G89" s="78"/>
+      <c r="H89" s="78"/>
+      <c r="I89" s="78"/>
     </row>
     <row r="90" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="82" t="s">
-        <v>88</v>
-      </c>
-      <c r="B90" s="82"/>
-      <c r="C90" s="82"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="82"/>
-      <c r="I90" s="82"/>
+      <c r="A90" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="B90" s="78"/>
+      <c r="C90" s="78"/>
+      <c r="D90" s="78"/>
+      <c r="E90" s="78"/>
+      <c r="F90" s="78"/>
+      <c r="G90" s="78"/>
+      <c r="H90" s="78"/>
+      <c r="I90" s="78"/>
     </row>
     <row r="91" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="82" t="s">
-        <v>87</v>
-      </c>
-      <c r="B91" s="82"/>
-      <c r="C91" s="82"/>
-      <c r="D91" s="82"/>
-      <c r="E91" s="82"/>
-      <c r="F91" s="82"/>
-      <c r="G91" s="82"/>
-      <c r="H91" s="82"/>
-      <c r="I91" s="82"/>
+      <c r="A91" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="B91" s="78"/>
+      <c r="C91" s="78"/>
+      <c r="D91" s="78"/>
+      <c r="E91" s="78"/>
+      <c r="F91" s="78"/>
+      <c r="G91" s="78"/>
+      <c r="H91" s="78"/>
+      <c r="I91" s="78"/>
     </row>
     <row r="92" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="B92" s="83"/>
-      <c r="C92" s="83"/>
-      <c r="D92" s="83"/>
-      <c r="E92" s="83"/>
-      <c r="F92" s="83"/>
-      <c r="G92" s="83"/>
-      <c r="H92" s="83"/>
-      <c r="I92" s="83"/>
+      <c r="A92" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" s="87"/>
+      <c r="C92" s="87"/>
+      <c r="D92" s="87"/>
+      <c r="E92" s="87"/>
+      <c r="F92" s="87"/>
+      <c r="G92" s="87"/>
+      <c r="H92" s="87"/>
+      <c r="I92" s="87"/>
     </row>
     <row r="93" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="83" t="s">
-        <v>85</v>
-      </c>
-      <c r="B93" s="83"/>
-      <c r="C93" s="83"/>
-      <c r="D93" s="83"/>
-      <c r="E93" s="83"/>
-      <c r="F93" s="83"/>
-      <c r="G93" s="83"/>
-      <c r="H93" s="83"/>
-      <c r="I93" s="83"/>
+      <c r="A93" s="87" t="s">
+        <v>84</v>
+      </c>
+      <c r="B93" s="87"/>
+      <c r="C93" s="87"/>
+      <c r="D93" s="87"/>
+      <c r="E93" s="87"/>
+      <c r="F93" s="87"/>
+      <c r="G93" s="87"/>
+      <c r="H93" s="87"/>
+      <c r="I93" s="87"/>
     </row>
     <row r="94" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B94" s="77"/>
-      <c r="C94" s="77"/>
-      <c r="D94" s="77"/>
-      <c r="E94" s="77"/>
-      <c r="F94" s="77"/>
-      <c r="G94" s="77"/>
-      <c r="H94" s="77"/>
-      <c r="I94" s="77"/>
+      <c r="A94" s="82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B94" s="82"/>
+      <c r="C94" s="82"/>
+      <c r="D94" s="82"/>
+      <c r="E94" s="82"/>
+      <c r="F94" s="82"/>
+      <c r="G94" s="82"/>
+      <c r="H94" s="82"/>
+      <c r="I94" s="82"/>
     </row>
     <row r="95" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B95" s="93"/>
       <c r="C95" s="93"/>
@@ -2916,125 +2937,125 @@
       <c r="I95" s="93"/>
     </row>
     <row r="96" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="82" t="s">
-        <v>82</v>
-      </c>
-      <c r="B96" s="82"/>
-      <c r="C96" s="82"/>
-      <c r="D96" s="82"/>
-      <c r="E96" s="82"/>
-      <c r="F96" s="82"/>
-      <c r="G96" s="82"/>
-      <c r="H96" s="82"/>
-      <c r="I96" s="82"/>
+      <c r="A96" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B96" s="78"/>
+      <c r="C96" s="78"/>
+      <c r="D96" s="78"/>
+      <c r="E96" s="78"/>
+      <c r="F96" s="78"/>
+      <c r="G96" s="78"/>
+      <c r="H96" s="78"/>
+      <c r="I96" s="78"/>
     </row>
     <row r="97" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="82" t="s">
-        <v>81</v>
-      </c>
-      <c r="B97" s="82"/>
-      <c r="C97" s="82"/>
-      <c r="D97" s="82"/>
-      <c r="E97" s="82"/>
-      <c r="F97" s="82"/>
-      <c r="G97" s="82"/>
-      <c r="H97" s="82"/>
-      <c r="I97" s="82"/>
+      <c r="A97" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B97" s="78"/>
+      <c r="C97" s="78"/>
+      <c r="D97" s="78"/>
+      <c r="E97" s="78"/>
+      <c r="F97" s="78"/>
+      <c r="G97" s="78"/>
+      <c r="H97" s="78"/>
+      <c r="I97" s="78"/>
     </row>
     <row r="98" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B98" s="82"/>
-      <c r="C98" s="82"/>
-      <c r="D98" s="82"/>
-      <c r="E98" s="82"/>
-      <c r="F98" s="82"/>
-      <c r="G98" s="82"/>
-      <c r="H98" s="82"/>
-      <c r="I98" s="82"/>
+      <c r="A98" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="B98" s="78"/>
+      <c r="C98" s="78"/>
+      <c r="D98" s="78"/>
+      <c r="E98" s="78"/>
+      <c r="F98" s="78"/>
+      <c r="G98" s="78"/>
+      <c r="H98" s="78"/>
+      <c r="I98" s="78"/>
     </row>
     <row r="99" spans="1:9" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="82" t="s">
-        <v>79</v>
-      </c>
-      <c r="B99" s="82"/>
-      <c r="C99" s="82"/>
-      <c r="D99" s="82"/>
-      <c r="E99" s="82"/>
-      <c r="F99" s="82"/>
-      <c r="G99" s="82"/>
-      <c r="H99" s="82"/>
-      <c r="I99" s="82"/>
+      <c r="A99" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B99" s="78"/>
+      <c r="C99" s="78"/>
+      <c r="D99" s="78"/>
+      <c r="E99" s="78"/>
+      <c r="F99" s="78"/>
+      <c r="G99" s="78"/>
+      <c r="H99" s="78"/>
+      <c r="I99" s="78"/>
     </row>
     <row r="100" spans="1:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="82" t="s">
-        <v>78</v>
-      </c>
-      <c r="B100" s="82"/>
-      <c r="C100" s="82"/>
-      <c r="D100" s="82"/>
-      <c r="E100" s="82"/>
-      <c r="F100" s="82"/>
-      <c r="G100" s="82"/>
-      <c r="H100" s="82"/>
-      <c r="I100" s="82"/>
+      <c r="A100" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B100" s="78"/>
+      <c r="C100" s="78"/>
+      <c r="D100" s="78"/>
+      <c r="E100" s="78"/>
+      <c r="F100" s="78"/>
+      <c r="G100" s="78"/>
+      <c r="H100" s="78"/>
+      <c r="I100" s="78"/>
     </row>
     <row r="101" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="77" t="s">
-        <v>77</v>
-      </c>
-      <c r="B101" s="77"/>
-      <c r="C101" s="77"/>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
-      <c r="F101" s="77"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="77"/>
-      <c r="I101" s="77"/>
+      <c r="A101" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="B101" s="82"/>
+      <c r="C101" s="82"/>
+      <c r="D101" s="82"/>
+      <c r="E101" s="82"/>
+      <c r="F101" s="82"/>
+      <c r="G101" s="82"/>
+      <c r="H101" s="82"/>
+      <c r="I101" s="82"/>
     </row>
     <row r="102" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="82" t="s">
-        <v>76</v>
-      </c>
-      <c r="B102" s="82"/>
-      <c r="C102" s="82"/>
-      <c r="D102" s="82"/>
-      <c r="E102" s="82"/>
-      <c r="F102" s="82"/>
-      <c r="G102" s="82"/>
-      <c r="H102" s="82"/>
-      <c r="I102" s="82"/>
+      <c r="A102" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="B102" s="78"/>
+      <c r="C102" s="78"/>
+      <c r="D102" s="78"/>
+      <c r="E102" s="78"/>
+      <c r="F102" s="78"/>
+      <c r="G102" s="78"/>
+      <c r="H102" s="78"/>
+      <c r="I102" s="78"/>
     </row>
     <row r="103" spans="1:9" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="82" t="s">
-        <v>75</v>
-      </c>
-      <c r="B103" s="82"/>
-      <c r="C103" s="82"/>
-      <c r="D103" s="82"/>
-      <c r="E103" s="82"/>
-      <c r="F103" s="82"/>
-      <c r="G103" s="82"/>
-      <c r="H103" s="82"/>
-      <c r="I103" s="82"/>
+      <c r="A103" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="B103" s="78"/>
+      <c r="C103" s="78"/>
+      <c r="D103" s="78"/>
+      <c r="E103" s="78"/>
+      <c r="F103" s="78"/>
+      <c r="G103" s="78"/>
+      <c r="H103" s="78"/>
+      <c r="I103" s="78"/>
     </row>
     <row r="104" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="82" t="s">
-        <v>74</v>
-      </c>
-      <c r="B104" s="82"/>
-      <c r="C104" s="82"/>
-      <c r="D104" s="82"/>
-      <c r="E104" s="82"/>
-      <c r="F104" s="82"/>
-      <c r="G104" s="82"/>
-      <c r="H104" s="82"/>
-      <c r="I104" s="82"/>
-    </row>
-    <row r="105" spans="1:9" s="61" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="78" t="s">
+        <v>73</v>
+      </c>
+      <c r="B104" s="78"/>
+      <c r="C104" s="78"/>
+      <c r="D104" s="78"/>
+      <c r="E104" s="78"/>
+      <c r="F104" s="78"/>
+      <c r="G104" s="78"/>
+      <c r="H104" s="78"/>
+      <c r="I104" s="78"/>
+    </row>
+    <row r="105" spans="1:9" s="60" customFormat="1" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="110" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B105" s="110"/>
       <c r="C105" s="110"/>
@@ -3046,47 +3067,47 @@
       <c r="I105" s="110"/>
     </row>
     <row r="106" spans="1:9" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="82" t="s">
-        <v>145</v>
-      </c>
-      <c r="B106" s="82"/>
-      <c r="C106" s="82"/>
-      <c r="D106" s="82"/>
-      <c r="E106" s="82"/>
-      <c r="F106" s="82"/>
-      <c r="G106" s="82"/>
-      <c r="H106" s="82"/>
-      <c r="I106" s="82"/>
+      <c r="A106" s="78" t="s">
+        <v>144</v>
+      </c>
+      <c r="B106" s="78"/>
+      <c r="C106" s="78"/>
+      <c r="D106" s="78"/>
+      <c r="E106" s="78"/>
+      <c r="F106" s="78"/>
+      <c r="G106" s="78"/>
+      <c r="H106" s="78"/>
+      <c r="I106" s="78"/>
     </row>
     <row r="107" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="82" t="s">
-        <v>73</v>
-      </c>
-      <c r="B107" s="82"/>
-      <c r="C107" s="82"/>
-      <c r="D107" s="82"/>
-      <c r="E107" s="82"/>
-      <c r="F107" s="82"/>
-      <c r="G107" s="82"/>
-      <c r="H107" s="82"/>
-      <c r="I107" s="82"/>
+      <c r="A107" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="B107" s="78"/>
+      <c r="C107" s="78"/>
+      <c r="D107" s="78"/>
+      <c r="E107" s="78"/>
+      <c r="F107" s="78"/>
+      <c r="G107" s="78"/>
+      <c r="H107" s="78"/>
+      <c r="I107" s="78"/>
     </row>
     <row r="108" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="B108" s="82"/>
-      <c r="C108" s="82"/>
-      <c r="D108" s="82"/>
-      <c r="E108" s="82"/>
-      <c r="F108" s="82"/>
-      <c r="G108" s="82"/>
-      <c r="H108" s="82"/>
-      <c r="I108" s="82"/>
+      <c r="A108" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B108" s="78"/>
+      <c r="C108" s="78"/>
+      <c r="D108" s="78"/>
+      <c r="E108" s="78"/>
+      <c r="F108" s="78"/>
+      <c r="G108" s="78"/>
+      <c r="H108" s="78"/>
+      <c r="I108" s="78"/>
     </row>
     <row r="109" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B109" s="95"/>
       <c r="C109" s="95"/>
@@ -3106,7 +3127,7 @@
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="112" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G110" s="112"/>
       <c r="H110" s="112"/>
@@ -3114,140 +3135,140 @@
     </row>
     <row r="111" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="109" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B111" s="109"/>
       <c r="C111" s="109"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="60"/>
-      <c r="G111" s="60"/>
-      <c r="H111" s="60"/>
-      <c r="I111" s="60"/>
+      <c r="F111" s="59"/>
+      <c r="G111" s="59"/>
+      <c r="H111" s="59"/>
+      <c r="I111" s="59"/>
     </row>
     <row r="112" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="98" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B112" s="98"/>
       <c r="C112" s="98"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="39" t="s">
-        <v>69</v>
+      <c r="F112" s="38" t="s">
+        <v>68</v>
       </c>
       <c r="G112" s="99" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H112" s="99"/>
       <c r="I112" s="99"/>
     </row>
     <row r="113" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="78" t="s">
-        <v>68</v>
-      </c>
-      <c r="B113" s="78"/>
-      <c r="C113" s="78"/>
+      <c r="A113" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="B113" s="83"/>
+      <c r="C113" s="83"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G113" s="65" t="s">
+      <c r="F113" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G113" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="H113" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="I113" s="64" t="s">
         <v>185</v>
-      </c>
-      <c r="H113" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="I113" s="65" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="98" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B114" s="98"/>
       <c r="C114" s="98"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G114" s="104"/>
       <c r="H114" s="104"/>
       <c r="I114" s="104"/>
     </row>
     <row r="115" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="B115" s="78"/>
-      <c r="C115" s="78"/>
+      <c r="A115" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="B115" s="83"/>
+      <c r="C115" s="83"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="108" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G115" s="108"/>
       <c r="H115" s="108"/>
       <c r="I115" s="108"/>
     </row>
     <row r="116" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="78" t="s">
-        <v>63</v>
-      </c>
-      <c r="B116" s="78"/>
-      <c r="C116" s="78"/>
+      <c r="A116" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B116" s="83"/>
+      <c r="C116" s="83"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="37"/>
-      <c r="G116" s="40"/>
-      <c r="H116" s="40"/>
-      <c r="I116" s="40"/>
+      <c r="F116" s="36"/>
+      <c r="G116" s="39"/>
+      <c r="H116" s="39"/>
+      <c r="I116" s="39"/>
     </row>
     <row r="117" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B117" s="78"/>
-      <c r="C117" s="78"/>
+      <c r="A117" s="83" t="s">
+        <v>61</v>
+      </c>
+      <c r="B117" s="83"/>
+      <c r="C117" s="83"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="104" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G117" s="104"/>
       <c r="H117" s="106" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I117" s="107"/>
     </row>
     <row r="118" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="78" t="s">
-        <v>60</v>
-      </c>
-      <c r="B118" s="78"/>
-      <c r="C118" s="78"/>
+      <c r="A118" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="B118" s="83"/>
+      <c r="C118" s="83"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="102" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G118" s="102"/>
-      <c r="H118" s="40"/>
-      <c r="I118" s="40"/>
+      <c r="H118" s="39"/>
+      <c r="I118" s="39"/>
     </row>
     <row r="119" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="78" t="s">
-        <v>176</v>
-      </c>
-      <c r="B119" s="78"/>
-      <c r="C119" s="78"/>
+      <c r="A119" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="B119" s="83"/>
+      <c r="C119" s="83"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="103" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G119" s="103"/>
       <c r="H119" s="103"/>
@@ -3255,7 +3276,7 @@
     </row>
     <row r="120" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="98" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B120" s="98"/>
       <c r="C120" s="98"/>
@@ -3267,118 +3288,118 @@
       <c r="I120" s="104"/>
     </row>
     <row r="121" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="69" t="s">
-        <v>56</v>
+      <c r="A121" s="68" t="s">
+        <v>55</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C121" s="15"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="102" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G121" s="102"/>
       <c r="H121" s="102"/>
-      <c r="I121" s="40"/>
+      <c r="I121" s="39"/>
     </row>
     <row r="122" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="69" t="s">
-        <v>177</v>
+      <c r="A122" s="68" t="s">
+        <v>176</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C122" s="69"/>
+        <v>194</v>
+      </c>
+      <c r="C122" s="68"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="25"/>
-      <c r="G122" s="40"/>
-      <c r="H122" s="40"/>
-      <c r="I122" s="40"/>
+      <c r="F122" s="24"/>
+      <c r="G122" s="39"/>
+      <c r="H122" s="39"/>
+      <c r="I122" s="39"/>
     </row>
     <row r="123" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="78" t="s">
-        <v>178</v>
-      </c>
-      <c r="B123" s="78"/>
-      <c r="C123" s="53" t="s">
-        <v>196</v>
+      <c r="A123" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="B123" s="83"/>
+      <c r="C123" s="52" t="s">
+        <v>195</v>
       </c>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
-      <c r="F123" s="67" t="s">
-        <v>184</v>
-      </c>
-      <c r="G123" s="40"/>
-      <c r="H123" s="40"/>
-      <c r="I123" s="40"/>
+      <c r="F123" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="G123" s="39"/>
+      <c r="H123" s="39"/>
+      <c r="I123" s="39"/>
     </row>
     <row r="124" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="78" t="s">
-        <v>57</v>
-      </c>
-      <c r="B124" s="78"/>
-      <c r="C124" s="78"/>
+      <c r="A124" s="83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" s="83"/>
+      <c r="C124" s="83"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="G124" s="40"/>
-      <c r="H124" s="40"/>
-      <c r="I124" s="40"/>
+      <c r="F124" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="G124" s="39"/>
+      <c r="H124" s="39"/>
+      <c r="I124" s="39"/>
     </row>
     <row r="125" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="B125" s="78"/>
-      <c r="C125" s="78"/>
+      <c r="A125" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="B125" s="83"/>
+      <c r="C125" s="83"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="66" t="s">
-        <v>204</v>
-      </c>
-      <c r="G125" s="58"/>
-      <c r="H125" s="58"/>
-      <c r="I125" s="58"/>
+      <c r="F125" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="G125" s="57"/>
+      <c r="H125" s="57"/>
+      <c r="I125" s="57"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B126" s="105"/>
       <c r="C126" s="105"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
-      <c r="F126" s="57"/>
-      <c r="G126" s="57"/>
-      <c r="H126" s="57"/>
-      <c r="I126" s="57"/>
+      <c r="F126" s="56"/>
+      <c r="G126" s="56"/>
+      <c r="H126" s="56"/>
+      <c r="I126" s="56"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B127" s="48" t="s">
-        <v>197</v>
+      <c r="B127" s="47" t="s">
+        <v>196</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="27"/>
-      <c r="G127" s="34"/>
-      <c r="H127" s="27"/>
-      <c r="I127" s="27"/>
+      <c r="F127" s="26"/>
+      <c r="G127" s="33"/>
+      <c r="H127" s="26"/>
+      <c r="I127" s="26"/>
     </row>
     <row r="128" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B128" s="48" t="s">
-        <v>198</v>
+        <v>178</v>
+      </c>
+      <c r="B128" s="47" t="s">
+        <v>197</v>
       </c>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -3389,10 +3410,10 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B129" s="48" t="s">
-        <v>199</v>
+        <v>179</v>
+      </c>
+      <c r="B129" s="47" t="s">
+        <v>198</v>
       </c>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -3406,7 +3427,7 @@
         <v>45</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -3421,23 +3442,23 @@
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
-      <c r="F131" s="27"/>
-      <c r="G131" s="27"/>
-      <c r="H131" s="27"/>
-      <c r="I131" s="27"/>
+      <c r="F131" s="26"/>
+      <c r="G131" s="26"/>
+      <c r="H131" s="26"/>
+      <c r="I131" s="26"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="48" t="s">
-        <v>201</v>
+      <c r="A132" s="47" t="s">
+        <v>200</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="27"/>
-      <c r="G132" s="27"/>
-      <c r="H132" s="27"/>
-      <c r="I132" s="27"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+      <c r="H132" s="26"/>
+      <c r="I132" s="26"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
@@ -3448,16 +3469,16 @@
       <c r="F133" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G133" s="68" t="s">
-        <v>183</v>
-      </c>
-      <c r="H133" s="56"/>
-      <c r="I133" s="56"/>
+      <c r="G133" s="67" t="s">
+        <v>182</v>
+      </c>
+      <c r="H133" s="55"/>
+      <c r="I133" s="55"/>
     </row>
     <row r="134" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
-      <c r="B134" s="48" t="s">
-        <v>202</v>
+      <c r="B134" s="47" t="s">
+        <v>201</v>
       </c>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
@@ -3467,7 +3488,7 @@
       </c>
       <c r="G134" s="10"/>
       <c r="H134" s="97" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I134" s="97"/>
     </row>
@@ -3643,7 +3664,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -3688,7 +3709,7 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G3" s="113"/>
       <c r="H3" s="113"/>
@@ -3700,11 +3721,11 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="97" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G4" s="97"/>
-      <c r="H4" s="50" t="s">
-        <v>182</v>
+      <c r="H4" s="49" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3720,7 +3741,7 @@
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="B6" s="121" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="121"/>
       <c r="D6" s="121"/>
@@ -3729,370 +3750,325 @@
       <c r="G6" s="121"/>
       <c r="H6" s="10"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" spans="1:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B8" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C8" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D8" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E8" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F8" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G8" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="20"/>
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>1</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="41"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="41" t="s">
+        <v>38</v>
+      </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="90" x14ac:dyDescent="0.25">
-      <c r="A10" s="21">
-        <v>1</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="20"/>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="141"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="20"/>
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="44" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="141"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="20"/>
-      <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="20"/>
-      <c r="J13" s="4"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="16"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="20"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="20"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="116" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="21"/>
-      <c r="H16" s="20"/>
-      <c r="J16" s="4"/>
+      <c r="A14" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="114"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+    </row>
+    <row r="15" spans="1:10" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="119" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="119"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
+      <c r="A17" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>196</v>
+      </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
+      <c r="E17" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>186</v>
+      </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="16"/>
+      <c r="E18" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="F18" s="89"/>
+      <c r="G18" s="89"/>
+      <c r="H18" s="89"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="114"/>
-      <c r="C19" s="114"/>
+      <c r="A19" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="114" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="114"/>
-      <c r="G19" s="114"/>
-      <c r="H19" s="114"/>
-    </row>
-    <row r="20" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="119" t="s">
-        <v>191</v>
-      </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
+      <c r="E19" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="120" t="s">
+        <v>192</v>
+      </c>
+      <c r="B20" s="120"/>
+      <c r="C20" s="120"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="49" t="s">
+      <c r="E20" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="48" t="s">
-        <v>200</v>
+        <v>11</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>193</v>
       </c>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>197</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F21" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
-      <c r="E22" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
+    <row r="23" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="71" t="s">
+        <v>201</v>
+      </c>
       <c r="D23" s="10"/>
-      <c r="E23" s="85" t="s">
-        <v>207</v>
-      </c>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
+      <c r="E23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="H23" s="31"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>8</v>
-      </c>
+      <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
-      <c r="E24" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="120" t="s">
-        <v>193</v>
-      </c>
-      <c r="B25" s="120"/>
-      <c r="C25" s="120"/>
+      <c r="A25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="115" t="s">
-        <v>184</v>
-      </c>
-      <c r="F25" s="115"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="115"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>194</v>
-      </c>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
-      <c r="E26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>204</v>
-      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
     </row>
-    <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="72" t="s">
-        <v>202</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="H28" s="32"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A25:C25"/>
     <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
     <mergeCell ref="F4:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="56" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4101,7 +4077,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -4124,7 +4100,7 @@
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="135" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H1" s="135"/>
       <c r="I1" s="135"/>
@@ -4137,7 +4113,7 @@
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="134" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H2" s="134"/>
       <c r="I2" s="134"/>
@@ -4150,11 +4126,11 @@
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="139" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H3" s="139"/>
-      <c r="I3" s="50" t="s">
-        <v>182</v>
+      <c r="I3" s="49" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -4184,7 +4160,7 @@
       <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="32" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="10"/>
@@ -4193,8 +4169,8 @@
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="51" t="s">
-        <v>189</v>
+      <c r="H6" s="50" t="s">
+        <v>188</v>
       </c>
       <c r="I6" s="10"/>
     </row>
@@ -4205,22 +4181,22 @@
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="20"/>
+      <c r="G7" s="19"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:10" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="80"/>
+      <c r="A8" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="138" t="s">
@@ -4228,7 +4204,7 @@
       </c>
       <c r="B9" s="138"/>
       <c r="C9" s="137" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D9" s="137"/>
       <c r="E9" s="137"/>
@@ -4243,29 +4219,29 @@
       </c>
       <c r="B10" s="138"/>
       <c r="C10" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="51" t="s">
         <v>186</v>
-      </c>
-      <c r="F10" s="34" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="52" t="s">
-        <v>187</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
+        <v>202</v>
+      </c>
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
@@ -4279,14 +4255,14 @@
       </c>
       <c r="B12" s="129"/>
       <c r="C12" s="129"/>
-      <c r="D12" s="85" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
+      <c r="D12" s="89" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="89"/>
+      <c r="I12" s="89"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="136" t="s">
@@ -4302,15 +4278,15 @@
       <c r="I13" s="136"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
     </row>
     <row r="15" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="123" t="s">
@@ -4326,7 +4302,7 @@
       <c r="I15" s="123"/>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="124" t="s">
@@ -4335,21 +4311,25 @@
       <c r="C16" s="124"/>
       <c r="D16" s="124"/>
       <c r="E16" s="124"/>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="4"/>
+      <c r="I16" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="140" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="41">
-        <f>Перечень!A10</f>
+      <c r="A17" s="40">
+        <f>Перечень!A9</f>
         <v>1</v>
       </c>
       <c r="B17" s="131" t="s">
@@ -4358,316 +4338,324 @@
       <c r="C17" s="132"/>
       <c r="D17" s="132"/>
       <c r="E17" s="133"/>
-      <c r="F17" s="41" t="s">
+      <c r="F17" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="41" t="s">
-        <v>49</v>
+      <c r="H17" s="40" t="s">
+        <v>48</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
+      <c r="A18" s="20" t="s">
+        <v>207</v>
+      </c>
       <c r="B18" s="125"/>
       <c r="C18" s="126"/>
       <c r="D18" s="126"/>
       <c r="E18" s="127"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="9"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="125"/>
-      <c r="C19" s="126"/>
-      <c r="D19" s="126"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+    <row r="19" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="116" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="40" t="s">
+        <v>48</v>
+      </c>
       <c r="I19" s="9"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="21"/>
-      <c r="B20" s="125"/>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="9"/>
+    <row r="20" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="129" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="129"/>
+      <c r="C20" s="129"/>
+      <c r="D20" s="129"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="129"/>
+      <c r="I20" s="129"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="21"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="9"/>
+    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="35" t="str">
+        <f>H19</f>
+        <v>цена услуг с НДС</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="130" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="130"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="130"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21"/>
-      <c r="B22" s="116" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="9"/>
+    <row r="22" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="128"/>
+      <c r="B22" s="128"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="128"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="129" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="129"/>
-      <c r="C23" s="129"/>
-      <c r="D23" s="129"/>
-      <c r="E23" s="129"/>
-      <c r="F23" s="129"/>
-      <c r="G23" s="129"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="129"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="str">
-        <f>H22</f>
-        <v>цена услуг с НДС</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="130" t="s">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="123" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="123"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="123"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+    </row>
+    <row r="24" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="123" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="123"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="123"/>
+    </row>
+    <row r="25" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="123" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="123"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
+      <c r="H25" s="123"/>
+      <c r="I25" s="123"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="114"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="114" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="114"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
+    </row>
+    <row r="28" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="85" t="s">
         <v>190</v>
       </c>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="128"/>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="128"/>
-      <c r="I25" s="128"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="123" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="123"/>
-      <c r="C26" s="123"/>
-      <c r="D26" s="123"/>
-      <c r="E26" s="123"/>
-      <c r="F26" s="123"/>
-      <c r="G26" s="123"/>
-      <c r="H26" s="123"/>
-      <c r="I26" s="123"/>
-    </row>
-    <row r="27" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="123" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="123"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="123"/>
-      <c r="G27" s="123"/>
-      <c r="H27" s="123"/>
-      <c r="I27" s="123"/>
-    </row>
-    <row r="28" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="123" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" s="123"/>
-      <c r="C28" s="123"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="123"/>
-      <c r="G28" s="123"/>
-      <c r="H28" s="123"/>
-      <c r="I28" s="123"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
+      <c r="D28" s="85"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="99" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="99"/>
+      <c r="I28" s="99"/>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>199</v>
+      </c>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="114" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="114"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="114" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-    </row>
-    <row r="31" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="80" t="s">
-        <v>191</v>
-      </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
-      <c r="D31" s="80"/>
+      <c r="F29" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="E31" s="10"/>
-      <c r="F31" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="99" t="s">
-        <v>183</v>
-      </c>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
-    </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B32" s="48" t="s">
-        <v>200</v>
-      </c>
+      <c r="F31" s="89" t="s">
+        <v>202</v>
+      </c>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="10"/>
       <c r="C32" s="10"/>
       <c r="D32" s="10"/>
       <c r="E32" s="10"/>
-      <c r="F32" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H32" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
+      <c r="F32" s="122" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="122"/>
+      <c r="H32" s="122"/>
+      <c r="I32" s="122"/>
+    </row>
+    <row r="33" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
       <c r="E33" s="10"/>
-      <c r="F33" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-    </row>
-    <row r="34" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
+      <c r="F33" s="98" t="s">
+        <v>183</v>
+      </c>
+      <c r="G33" s="98"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="98"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>193</v>
+      </c>
       <c r="C34" s="10"/>
-      <c r="D34" s="10" t="s">
-        <v>24</v>
-      </c>
+      <c r="D34" s="10"/>
       <c r="E34" s="10"/>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="G34" s="85"/>
-      <c r="H34" s="85"/>
-      <c r="I34" s="85"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
-        <v>8</v>
-      </c>
       <c r="B35" s="10"/>
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="122" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="122"/>
-      <c r="H35" s="122"/>
-      <c r="I35" s="122"/>
-    </row>
-    <row r="36" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="D36" s="10"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="98" t="s">
-        <v>184</v>
-      </c>
-      <c r="G36" s="98"/>
-      <c r="H36" s="98"/>
-      <c r="I36" s="98"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="48" t="s">
-        <v>194</v>
-      </c>
+      <c r="F36" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+    </row>
+    <row r="37" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="26"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
+      <c r="D37" s="47" t="s">
+        <v>201</v>
+      </c>
       <c r="E37" s="10"/>
       <c r="F37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="97" t="s">
+        <v>182</v>
+      </c>
+      <c r="I37" s="97"/>
+    </row>
+    <row r="38" spans="1:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
@@ -4678,62 +4666,20 @@
       <c r="I38" s="10"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="48" t="s">
-        <v>201</v>
+      <c r="A39" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="28" t="s">
-        <v>29</v>
-      </c>
+      <c r="F39" s="10"/>
       <c r="G39" s="10"/>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
     </row>
-    <row r="40" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="27"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" s="10"/>
-      <c r="H40" s="97" t="s">
-        <v>183</v>
-      </c>
-      <c r="I40" s="97"/>
-    </row>
-    <row r="41" spans="1:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="31">
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="C5:H5"/>
@@ -4746,28 +4692,25 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F34:I34"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="F30:I30"/>
-    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="F32:I32"/>
+    <mergeCell ref="F31:I31"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="F33:I33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="portrait" r:id="rId1"/>
